--- a/edu.xlsx
+++ b/edu.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11535"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="320">
   <si>
     <t>种类</t>
   </si>
@@ -1217,6 +1217,41 @@
   </si>
   <si>
     <t>hard</t>
+  </si>
+  <si>
+    <t>找性质</t>
+  </si>
+  <si>
+    <t>并查集+set</t>
+  </si>
+  <si>
+    <t>set存右端点 + 编号 按左端点排序 每次加新的进去 二分找能合并的点 
+超过n就是-1</t>
+  </si>
+  <si>
+    <t>D的构造</t>
+  </si>
+  <si>
+    <t>当前点的右端点坐标可以被确定 左端点倒着存</t>
+  </si>
+  <si>
+    <t>E，F</t>
+  </si>
+  <si>
+    <t>思维 + stl</t>
+  </si>
+  <si>
+    <t>推式子 概率</t>
+  </si>
+  <si>
+    <t>值域存下标 暴力统计</t>
+  </si>
+  <si>
+    <t>WQS二分 + DP</t>
+  </si>
+  <si>
+    <t>覆盖的时候 是一个凸函数
+考虑每次覆盖有一个代价 二分代价能二分到刚好 &lt;=k 次的时候 就是要的答案</t>
   </si>
 </sst>
 </file>
@@ -2209,7 +2244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ78"/>
+  <dimension ref="A1:AQ80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="11" customWidth="1"/>
@@ -8457,7 +8492,7 @@
       <c r="S78" t="s">
         <v>305</v>
       </c>
-      <c r="T78" s="9" t="s">
+      <c r="T78" s="3" t="s">
         <v>306</v>
       </c>
       <c r="U78" t="s">
@@ -8528,6 +8563,232 @@
       </c>
       <c r="AQ78">
         <v>77</v>
+      </c>
+    </row>
+    <row r="79" ht="30" spans="2:43">
+      <c r="B79">
+        <v>78</v>
+      </c>
+      <c r="D79">
+        <v>1278</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0.00277777777777778</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="I79" s="1">
+        <v>0.0131944444444444</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79" t="s">
+        <v>309</v>
+      </c>
+      <c r="M79" s="1">
+        <v>0.025</v>
+      </c>
+      <c r="N79">
+        <v>2</v>
+      </c>
+      <c r="O79" t="s">
+        <v>310</v>
+      </c>
+      <c r="P79" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="R79">
+        <v>1</v>
+      </c>
+      <c r="S79" t="s">
+        <v>312</v>
+      </c>
+      <c r="T79" t="s">
+        <v>313</v>
+      </c>
+      <c r="U79" t="s">
+        <v>22</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB79" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC79" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE79" t="s">
+        <v>314</v>
+      </c>
+      <c r="AF79" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG79">
+        <v>1000</v>
+      </c>
+      <c r="AH79">
+        <v>1500</v>
+      </c>
+      <c r="AI79">
+        <v>1700</v>
+      </c>
+      <c r="AJ79">
+        <v>2100</v>
+      </c>
+      <c r="AK79">
+        <v>2200</v>
+      </c>
+      <c r="AL79">
+        <v>2600</v>
+      </c>
+      <c r="AM79" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO79" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP79">
+        <v>1278</v>
+      </c>
+      <c r="AQ79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" ht="30" spans="2:43">
+      <c r="B80">
+        <v>79</v>
+      </c>
+      <c r="D80">
+        <v>1279</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0.00208333333333333</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
+      </c>
+      <c r="H80" t="s">
+        <v>30</v>
+      </c>
+      <c r="I80" s="1">
+        <v>0.00902777777777778</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80" t="s">
+        <v>315</v>
+      </c>
+      <c r="M80" s="1">
+        <v>0.0173611111111111</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80" t="s">
+        <v>316</v>
+      </c>
+      <c r="P80" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="R80">
+        <v>1</v>
+      </c>
+      <c r="S80" t="s">
+        <v>244</v>
+      </c>
+      <c r="U80" t="s">
+        <v>22</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80" t="s">
+        <v>318</v>
+      </c>
+      <c r="X80" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB80" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE80" t="s">
+        <v>314</v>
+      </c>
+      <c r="AF80" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG80">
+        <v>900</v>
+      </c>
+      <c r="AH80">
+        <v>1300</v>
+      </c>
+      <c r="AI80">
+        <v>1400</v>
+      </c>
+      <c r="AJ80">
+        <v>1700</v>
+      </c>
+      <c r="AK80">
+        <v>2700</v>
+      </c>
+      <c r="AL80">
+        <v>2800</v>
+      </c>
+      <c r="AM80" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO80" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP80">
+        <v>1279</v>
+      </c>
+      <c r="AQ80">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11535"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="328">
   <si>
     <t>种类</t>
   </si>
@@ -1252,6 +1252,30 @@
   <si>
     <t>覆盖的时候 是一个凸函数
 考虑每次覆盖有一个代价 二分代价能二分到刚好 &lt;=k 次的时候 就是要的答案</t>
+  </si>
+  <si>
+    <t>逆天题</t>
+  </si>
+  <si>
+    <t>打表</t>
+  </si>
+  <si>
+    <t>二位前缀和优化DP</t>
+  </si>
+  <si>
+    <t>二分+DP</t>
+  </si>
+  <si>
+    <t>枚举子集DP  两个集合合起来状态得是全集</t>
+  </si>
+  <si>
+    <t>算区间种类个数</t>
+  </si>
+  <si>
+    <t>HH的项链 翻版</t>
+  </si>
+  <si>
+    <t>最小费用可行流</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1926,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1929,9 +1953,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2244,7 +2265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ80"/>
+  <dimension ref="A1:AQ81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="11" customWidth="1"/>
@@ -8596,7 +8617,7 @@
       <c r="O79" t="s">
         <v>310</v>
       </c>
-      <c r="P79" s="9" t="s">
+      <c r="P79" s="3" t="s">
         <v>311</v>
       </c>
       <c r="Q79" s="1">
@@ -8730,7 +8751,7 @@
       <c r="W80" t="s">
         <v>318</v>
       </c>
-      <c r="X80" s="9" t="s">
+      <c r="X80" s="3" t="s">
         <v>319</v>
       </c>
       <c r="Y80" t="s">
@@ -8789,6 +8810,128 @@
       </c>
       <c r="AQ80">
         <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="2:43">
+      <c r="B81">
+        <v>80</v>
+      </c>
+      <c r="D81">
+        <v>1288</v>
+      </c>
+      <c r="E81" t="s">
+        <v>320</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0.0208333333333333</v>
+      </c>
+      <c r="G81">
+        <v>7</v>
+      </c>
+      <c r="H81" t="s">
+        <v>321</v>
+      </c>
+      <c r="I81" s="1">
+        <v>0.025</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81" t="s">
+        <v>244</v>
+      </c>
+      <c r="L81" t="s">
+        <v>322</v>
+      </c>
+      <c r="M81" s="1">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="O81" t="s">
+        <v>323</v>
+      </c>
+      <c r="P81" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>0.0520833333333333</v>
+      </c>
+      <c r="R81">
+        <v>1</v>
+      </c>
+      <c r="S81" t="s">
+        <v>325</v>
+      </c>
+      <c r="T81" t="s">
+        <v>326</v>
+      </c>
+      <c r="U81" s="1">
+        <v>0.0840277777777778</v>
+      </c>
+      <c r="V81">
+        <v>4</v>
+      </c>
+      <c r="W81" t="s">
+        <v>327</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB81" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC81" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE81" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF81" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG81">
+        <v>1100</v>
+      </c>
+      <c r="AH81">
+        <v>1100</v>
+      </c>
+      <c r="AI81">
+        <v>1600</v>
+      </c>
+      <c r="AJ81">
+        <v>2000</v>
+      </c>
+      <c r="AK81">
+        <v>2000</v>
+      </c>
+      <c r="AL81">
+        <v>2700</v>
+      </c>
+      <c r="AM81" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO81" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP81">
+        <v>1288</v>
+      </c>
+      <c r="AQ81">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11535"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="333">
   <si>
     <t>种类</t>
   </si>
@@ -1276,6 +1276,24 @@
   </si>
   <si>
     <t>最小费用可行流</t>
+  </si>
+  <si>
+    <t>观察到如果是无穷 当且仅当前缀和pre n 为0 并且中间有符合值
+否则每个位置最多贡献一次 考虑是否是前缀和pre n的倍数</t>
+  </si>
+  <si>
+    <t>SET</t>
+  </si>
+  <si>
+    <t>存26个set暴力二分下一个位置即可</t>
+  </si>
+  <si>
+    <t>容斥</t>
+  </si>
+  <si>
+    <t>枚举哪些质因子不能要，哪些质因子一定要
+一定要的数量 减去不能要的数量*一定要的数字 就是答案
+多个质因子相乘的时候用容斥 枚举二进制集合来做</t>
   </si>
 </sst>
 </file>
@@ -1926,7 +1944,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1953,6 +1971,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2265,10 +2286,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ81"/>
+  <dimension ref="A1:AQ82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="8" max="8" width="62.5714285714286" customWidth="1"/>
     <col min="11" max="11" width="15.247619047619" customWidth="1"/>
     <col min="12" max="12" width="39.5047619047619" customWidth="1"/>
     <col min="13" max="13" width="10.1238095238095" customWidth="1"/>
@@ -8932,6 +8953,116 @@
       </c>
       <c r="AQ81">
         <v>80</v>
+      </c>
+    </row>
+    <row r="82" ht="45" spans="2:43">
+      <c r="B82">
+        <v>81</v>
+      </c>
+      <c r="D82">
+        <v>1295</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0.000694444444444444</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I82" s="1">
+        <v>0.00902777777777778</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82" t="s">
+        <v>329</v>
+      </c>
+      <c r="L82" t="s">
+        <v>330</v>
+      </c>
+      <c r="M82" s="1">
+        <v>0.0173611111111111</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82" t="s">
+        <v>331</v>
+      </c>
+      <c r="P82" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>0.0506944444444444</v>
+      </c>
+      <c r="R82">
+        <v>1</v>
+      </c>
+      <c r="U82" t="s">
+        <v>22</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB82" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC82" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD82" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE82" t="s">
+        <v>314</v>
+      </c>
+      <c r="AF82" t="s">
+        <v>314</v>
+      </c>
+      <c r="AG82">
+        <v>900</v>
+      </c>
+      <c r="AH82">
+        <v>1700</v>
+      </c>
+      <c r="AI82">
+        <v>1600</v>
+      </c>
+      <c r="AJ82">
+        <v>1800</v>
+      </c>
+      <c r="AK82">
+        <v>2200</v>
+      </c>
+      <c r="AL82">
+        <v>2700</v>
+      </c>
+      <c r="AM82" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO82" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP82">
+        <v>1295</v>
+      </c>
+      <c r="AQ82">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11535"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="346">
   <si>
     <t>种类</t>
   </si>
@@ -1294,6 +1294,52 @@
     <t>枚举哪些质因子不能要，哪些质因子一定要
 一定要的数量 减去不能要的数量*一定要的数字 就是答案
 多个质因子相乘的时候用容斥 枚举二进制集合来做</t>
+  </si>
+  <si>
+    <t>欧拉路径森林</t>
+  </si>
+  <si>
+    <t>没有奇数度数的点直接NO
+否则从一个个奇数点度数开始搜索</t>
+  </si>
+  <si>
+    <t>二进制拆位+枚举</t>
+  </si>
+  <si>
+    <t>从小到大用完的可以往高位合并
+否则取下一个有1高位的位置 这样贪心最优 肯定比找更大的优
+因为最多都只需要一个</t>
+  </si>
+  <si>
+    <t>枚举分割点 S1 S2段的长度 
+dp ij 表示前i个位置 已经拼出前j个s1 的最大s2长度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">并查集 </t>
+  </si>
+  <si>
+    <t>SGT分治会被卡TLE
+考虑对每种颜色考虑 因为并查集合并每种颜色单独考虑就行 按时间存有的数字 当前有一个颜色的格子 就先+1 看左右有没有合并好的 与周围通后要减去1
+  由于颜色编号只会增大具有单调性   由此 正着做的时候 直接按这样做就行  删去的颜色怎么考虑 按时间倒着考虑即可 因为颜色也有单调性 与前面相反就行</t>
+  </si>
+  <si>
+    <t>李超树+点分治/链分治</t>
+  </si>
+  <si>
+    <t>转k进制拆位 每位单独考虑</t>
+  </si>
+  <si>
+    <t>简单组合数学</t>
+  </si>
+  <si>
+    <t xml:space="preserve">区间DP </t>
+  </si>
+  <si>
+    <t>dpij 代表当前 ij区间能否完全合并 和 当前合并后的值
+ansij 代表 当前ij区间最多能消除的个数 答案就是 n - ans 1,n</t>
+  </si>
+  <si>
+    <t>trie+DP</t>
   </si>
 </sst>
 </file>
@@ -2286,7 +2332,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ82"/>
+  <dimension ref="A1:AQ84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="62.5714285714286" customWidth="1"/>
@@ -8968,7 +9014,7 @@
       <c r="G82">
         <v>1</v>
       </c>
-      <c r="H82" s="9" t="s">
+      <c r="H82" s="3" t="s">
         <v>328</v>
       </c>
       <c r="I82" s="1">
@@ -8992,7 +9038,7 @@
       <c r="O82" t="s">
         <v>331</v>
       </c>
-      <c r="P82" s="9" t="s">
+      <c r="P82" s="3" t="s">
         <v>332</v>
       </c>
       <c r="Q82" s="1">
@@ -9063,6 +9109,235 @@
       </c>
       <c r="AQ82">
         <v>81</v>
+      </c>
+    </row>
+    <row r="83" ht="45" spans="2:43">
+      <c r="B83">
+        <v>82</v>
+      </c>
+      <c r="D83">
+        <v>1303</v>
+      </c>
+      <c r="F83" s="1">
+        <v>0.00277777777777778</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="I83" s="1">
+        <v>0.00625</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="K83" t="s">
+        <v>333</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="M83" s="1">
+        <v>0.01875</v>
+      </c>
+      <c r="N83">
+        <v>3</v>
+      </c>
+      <c r="O83" t="s">
+        <v>335</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q83" s="1">
+        <v>0.03125</v>
+      </c>
+      <c r="R83">
+        <v>1</v>
+      </c>
+      <c r="S83" t="s">
+        <v>181</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="U83" t="s">
+        <v>22</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83" t="s">
+        <v>338</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC83" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD83">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF83" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG83">
+        <v>800</v>
+      </c>
+      <c r="AH83">
+        <v>1400</v>
+      </c>
+      <c r="AI83">
+        <v>1600</v>
+      </c>
+      <c r="AJ83">
+        <v>1900</v>
+      </c>
+      <c r="AK83">
+        <v>2200</v>
+      </c>
+      <c r="AL83">
+        <v>2800</v>
+      </c>
+      <c r="AM83">
+        <v>2700</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO83" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP83">
+        <v>1303</v>
+      </c>
+      <c r="AQ83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" ht="30" spans="2:43">
+      <c r="B84">
+        <v>83</v>
+      </c>
+      <c r="D84">
+        <v>1312</v>
+      </c>
+      <c r="F84" s="1">
+        <v>0.00138888888888889</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="I84" s="1">
+        <v>0.00277777777777778</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84" t="s">
+        <v>169</v>
+      </c>
+      <c r="L84" t="s">
+        <v>341</v>
+      </c>
+      <c r="M84" s="1">
+        <v>0.0159722222222222</v>
+      </c>
+      <c r="N84">
+        <v>2</v>
+      </c>
+      <c r="O84" t="s">
+        <v>302</v>
+      </c>
+      <c r="P84" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q84" s="1">
+        <v>0.0326388888888889</v>
+      </c>
+      <c r="R84">
+        <v>1</v>
+      </c>
+      <c r="S84" t="s">
+        <v>343</v>
+      </c>
+      <c r="T84" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="U84" s="1">
+        <v>0.0701388888888889</v>
+      </c>
+      <c r="V84">
+        <v>5</v>
+      </c>
+      <c r="W84" t="s">
+        <v>280</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>345</v>
+      </c>
+      <c r="AC84" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD84">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF84" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG84">
+        <v>800</v>
+      </c>
+      <c r="AH84">
+        <v>1000</v>
+      </c>
+      <c r="AI84">
+        <v>1400</v>
+      </c>
+      <c r="AJ84">
+        <v>1700</v>
+      </c>
+      <c r="AK84">
+        <v>2100</v>
+      </c>
+      <c r="AL84">
+        <v>2500</v>
+      </c>
+      <c r="AM84">
+        <v>2600</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO84" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP84">
+        <v>1312</v>
+      </c>
+      <c r="AQ84">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11535"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="361">
   <si>
     <t>种类</t>
   </si>
@@ -1161,7 +1161,26 @@
     <t>倒着考虑的贪心 很智慧</t>
   </si>
   <si>
-    <t>数学，FFT，NTT</t>
+    <t>数学，NTT</t>
+  </si>
+  <si>
+    <t>周长 = (hmax + cnt) * 2
+题目中红板的数量极少（最多 5 个），且每种方案有且仅有一块红板作为最高板
+直接对每块红板单独计算贡献  只考虑高度严格小于当前红板高度的白板
+对于拥有 &gt;=2 块的同高度白板（设此类高度共有 b 种）
+选 0 块：1 种方案
+选 1 块：2 种方案（放左边或放右边）
+选 2 块：1 种方案（左右各放一个）
+该类白板的生成函数为：(1 + 2x + x^2)
+对于只有 1 块的同高度白板（设此类高度共有 a 种）
+选 0 块：1 种方案
+选 1 块：2 种方案（虽然只有一块，但逻辑上可以对应放在左侧上升序列或右侧下降序列，题目视为不同方案）
+该类白板的生成函数为：(1 + 2x)
+结合上述两类白板，对于高度小于红板的所有白板，其组合方案的整体多项式为
+F(x) = (1 + 2x)^a * (1 + 2x + x^2)^b
+F(x) = (1 + 2x)^a * (1 + x)^(2*b)
+二项式定理（Binomial Theorem）快速求出每一项的系数
+使用 NTT（快速数论变换）将两个多项式卷积合并，即可得到选出 j 块白板的总方案数</t>
   </si>
   <si>
     <t>数学观察</t>
@@ -1186,7 +1205,7 @@
   </si>
   <si>
     <t>拆位 前十五位和后十五位
-$$H_i(high) + L_i(low) = H_1(high) + L_1(low)$$  H是低位的15 L是高位的15
+Hi(high) + Li(low) = H1(high) + L1(low)  H是低位的15   L是高位的15
 移项后变成 Hi-H1 = L1 - Li</t>
   </si>
   <si>
@@ -1235,6 +1254,9 @@
     <t>当前点的右端点坐标可以被确定 左端点倒着存</t>
   </si>
   <si>
+    <t>？</t>
+  </si>
+  <si>
     <t>E，F</t>
   </si>
   <si>
@@ -1340,6 +1362,175 @@
   </si>
   <si>
     <t>trie+DP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>已经遇到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>cnt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次目标串</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+cost = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> pre </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>补全到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> u </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>得情况</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+cost = dp[pre] + ranku u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>pre</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>子树里面得排名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+cost = dp[pre] + cnt - precnt
+cost = cnt + dp[pre] - precnt</t>
+    </r>
+  </si>
+  <si>
+    <t>诈骗</t>
+  </si>
+  <si>
+    <t>全到左上角 后蛇形遍历</t>
+  </si>
+  <si>
+    <t>置换环</t>
+  </si>
+  <si>
+    <t>转图论 后变成求最小环问题</t>
+  </si>
+  <si>
+    <t>推式子 递推</t>
+  </si>
+  <si>
+    <t>画几个发现 倒着推就行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拆位 + DP </t>
+  </si>
+  <si>
+    <t>贪心 + 双指针</t>
+  </si>
+  <si>
+    <t>肯定是按顺序最优</t>
+  </si>
+  <si>
+    <t>完全图先1为起点12 13 14 .... 1n  再2 3 24 25... 2n</t>
+  </si>
+  <si>
+    <t>数论</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拆路径计数  多重集排列公式是 ans =(Σ因子)！ /  ∏ (因子！)
+  u 和 v的最短路一定会经过gcd uv  路径就是 gcd到u 的答案乘以 gcd到v的答案                                       </t>
   </si>
 </sst>
 </file>
@@ -2332,7 +2523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ84"/>
+  <dimension ref="A1:AQ86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="62.5714285714286" customWidth="1"/>
@@ -2348,7 +2539,7 @@
     <col min="24" max="24" width="145.371428571429" customWidth="1"/>
     <col min="25" max="25" width="12.3714285714286" customWidth="1"/>
     <col min="27" max="27" width="34.1238095238095" customWidth="1"/>
-    <col min="28" max="28" width="44.8761904761905" customWidth="1"/>
+    <col min="28" max="28" width="48.1428571428571" customWidth="1"/>
     <col min="30" max="30" width="7.75238095238095" customWidth="1"/>
     <col min="31" max="31" width="10.1238095238095" customWidth="1"/>
   </cols>
@@ -8311,7 +8502,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" ht="30" spans="2:43">
+    <row r="76" ht="255" spans="2:43">
       <c r="B76">
         <v>75</v>
       </c>
@@ -8363,6 +8554,9 @@
       <c r="W76" t="s">
         <v>292</v>
       </c>
+      <c r="X76" s="3" t="s">
+        <v>293</v>
+      </c>
       <c r="Y76" t="s">
         <v>22</v>
       </c>
@@ -8380,6 +8574,12 @@
       </c>
       <c r="AD76" t="s">
         <v>25</v>
+      </c>
+      <c r="AE76" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF76" t="s">
+        <v>276</v>
       </c>
       <c r="AG76">
         <v>1000</v>
@@ -8429,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I77" s="1">
         <v>0.0111111111111111</v>
@@ -8447,10 +8647,10 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q77" s="1">
         <v>0.0305555555555556</v>
@@ -8459,10 +8659,10 @@
         <v>2</v>
       </c>
       <c r="S77" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="T77" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="U77" t="s">
         <v>22</v>
@@ -8471,10 +8671,10 @@
         <v>-2</v>
       </c>
       <c r="W77" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="X77" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y77" t="s">
         <v>22</v>
@@ -8483,10 +8683,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AB77" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AC77" t="s">
         <v>22</v>
@@ -8554,10 +8754,10 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L78" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M78" s="1">
         <v>0.0506944444444444</v>
@@ -8569,7 +8769,7 @@
         <v>251</v>
       </c>
       <c r="P78" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q78" t="s">
         <v>22</v>
@@ -8578,10 +8778,10 @@
         <v>-8</v>
       </c>
       <c r="S78" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="T78" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="U78" t="s">
         <v>22</v>
@@ -8590,10 +8790,10 @@
         <v>0</v>
       </c>
       <c r="W78" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="X78" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y78" t="s">
         <v>22</v>
@@ -8673,7 +8873,7 @@
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M79" s="1">
         <v>0.025</v>
@@ -8682,10 +8882,10 @@
         <v>2</v>
       </c>
       <c r="O79" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q79" s="1">
         <v>0.0416666666666667</v>
@@ -8694,10 +8894,10 @@
         <v>1</v>
       </c>
       <c r="S79" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="T79" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="U79" t="s">
         <v>22</v>
@@ -8705,6 +8905,12 @@
       <c r="V79">
         <v>0</v>
       </c>
+      <c r="W79" t="s">
+        <v>315</v>
+      </c>
+      <c r="X79" t="s">
+        <v>309</v>
+      </c>
       <c r="Y79" t="s">
         <v>22</v>
       </c>
@@ -8724,7 +8930,7 @@
         <v>25</v>
       </c>
       <c r="AE79" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AF79" t="s">
         <v>11</v>
@@ -8786,7 +8992,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M80" s="1">
         <v>0.0173611111111111</v>
@@ -8795,10 +9001,10 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P80" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q80" s="1">
         <v>0.0326388888888889</v>
@@ -8816,10 +9022,10 @@
         <v>0</v>
       </c>
       <c r="W80" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="X80" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Y80" t="s">
         <v>22</v>
@@ -8840,7 +9046,7 @@
         <v>25</v>
       </c>
       <c r="AE80" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AF80" t="s">
         <v>10</v>
@@ -8887,7 +9093,7 @@
         <v>1288</v>
       </c>
       <c r="E81" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F81" s="1">
         <v>0.0208333333333333</v>
@@ -8896,7 +9102,7 @@
         <v>7</v>
       </c>
       <c r="H81" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I81" s="1">
         <v>0.025</v>
@@ -8908,7 +9114,7 @@
         <v>244</v>
       </c>
       <c r="L81" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M81" s="1">
         <v>0.0416666666666667</v>
@@ -8917,10 +9123,10 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P81" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q81" s="1">
         <v>0.0520833333333333</v>
@@ -8929,10 +9135,10 @@
         <v>1</v>
       </c>
       <c r="S81" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="T81" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="U81" s="1">
         <v>0.0840277777777778</v>
@@ -8941,7 +9147,10 @@
         <v>4</v>
       </c>
       <c r="W81" t="s">
-        <v>327</v>
+        <v>329</v>
+      </c>
+      <c r="X81" t="s">
+        <v>309</v>
       </c>
       <c r="Y81" t="s">
         <v>22</v>
@@ -9015,7 +9224,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I82" s="1">
         <v>0.00902777777777778</v>
@@ -9024,10 +9233,10 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L82" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M82" s="1">
         <v>0.0173611111111111</v>
@@ -9036,10 +9245,10 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q82" s="1">
         <v>0.0506944444444444</v>
@@ -9053,6 +9262,12 @@
       <c r="V82">
         <v>0</v>
       </c>
+      <c r="W82" t="s">
+        <v>315</v>
+      </c>
+      <c r="X82" t="s">
+        <v>309</v>
+      </c>
       <c r="Y82" t="s">
         <v>22</v>
       </c>
@@ -9072,10 +9287,10 @@
         <v>25</v>
       </c>
       <c r="AE82" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AF82" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG82">
         <v>900</v>
@@ -9131,10 +9346,10 @@
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M83" s="1">
         <v>0.01875</v>
@@ -9143,10 +9358,10 @@
         <v>3</v>
       </c>
       <c r="O83" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q83" s="1">
         <v>0.03125</v>
@@ -9158,7 +9373,7 @@
         <v>181</v>
       </c>
       <c r="T83" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="U83" t="s">
         <v>22</v>
@@ -9167,10 +9382,10 @@
         <v>0</v>
       </c>
       <c r="W83" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="X83" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Y83" t="s">
         <v>22</v>
@@ -9179,7 +9394,7 @@
         <v>0</v>
       </c>
       <c r="AA83" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AC83" t="s">
         <v>22</v>
@@ -9227,7 +9442,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" ht="30" spans="2:43">
+    <row r="84" ht="71.25" spans="2:43">
       <c r="B84">
         <v>83</v>
       </c>
@@ -9250,7 +9465,7 @@
         <v>169</v>
       </c>
       <c r="L84" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M84" s="1">
         <v>0.0159722222222222</v>
@@ -9259,10 +9474,10 @@
         <v>2</v>
       </c>
       <c r="O84" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P84" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q84" s="1">
         <v>0.0326388888888889</v>
@@ -9271,10 +9486,10 @@
         <v>1</v>
       </c>
       <c r="S84" t="s">
-        <v>343</v>
-      </c>
-      <c r="T84" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
+      </c>
+      <c r="T84" s="3" t="s">
+        <v>346</v>
       </c>
       <c r="U84" s="1">
         <v>0.0701388888888889</v>
@@ -9285,6 +9500,9 @@
       <c r="W84" t="s">
         <v>280</v>
       </c>
+      <c r="X84" t="s">
+        <v>309</v>
+      </c>
       <c r="Y84" t="s">
         <v>22</v>
       </c>
@@ -9292,7 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="s">
-        <v>345</v>
+        <v>347</v>
+      </c>
+      <c r="AB84" s="5" t="s">
+        <v>348</v>
       </c>
       <c r="AC84" t="s">
         <v>22</v>
@@ -9304,7 +9525,7 @@
         <v>137</v>
       </c>
       <c r="AF84" t="s">
-        <v>137</v>
+        <v>11</v>
       </c>
       <c r="AG84">
         <v>800</v>
@@ -9338,6 +9559,235 @@
       </c>
       <c r="AQ84">
         <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="2:43">
+      <c r="B85">
+        <v>84</v>
+      </c>
+      <c r="D85">
+        <v>1327</v>
+      </c>
+      <c r="F85" s="1">
+        <v>0.00138888888888889</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
+        <v>83</v>
+      </c>
+      <c r="I85" s="1">
+        <v>0.00486111111111111</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85" t="s">
+        <v>349</v>
+      </c>
+      <c r="L85" t="s">
+        <v>350</v>
+      </c>
+      <c r="M85" s="1">
+        <v>0.0277777777777778</v>
+      </c>
+      <c r="N85">
+        <v>4</v>
+      </c>
+      <c r="O85" t="s">
+        <v>351</v>
+      </c>
+      <c r="P85" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q85" s="1">
+        <v>0.0777777777777778</v>
+      </c>
+      <c r="R85">
+        <v>3</v>
+      </c>
+      <c r="S85" t="s">
+        <v>353</v>
+      </c>
+      <c r="T85" t="s">
+        <v>354</v>
+      </c>
+      <c r="U85" s="1">
+        <v>0.04375</v>
+      </c>
+      <c r="V85">
+        <v>2</v>
+      </c>
+      <c r="W85" t="s">
+        <v>355</v>
+      </c>
+      <c r="X85" t="s">
+        <v>309</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB85" t="s">
+        <v>309</v>
+      </c>
+      <c r="AC85" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD85">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF85" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG85">
+        <v>1100</v>
+      </c>
+      <c r="AH85">
+        <v>1200</v>
+      </c>
+      <c r="AI85">
+        <v>1600</v>
+      </c>
+      <c r="AJ85">
+        <v>2200</v>
+      </c>
+      <c r="AK85">
+        <v>1800</v>
+      </c>
+      <c r="AL85">
+        <v>2500</v>
+      </c>
+      <c r="AM85">
+        <v>2800</v>
+      </c>
+      <c r="AN85" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO85" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP85">
+        <v>1327</v>
+      </c>
+      <c r="AQ85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" ht="30" spans="2:43">
+      <c r="B86">
+        <v>85</v>
+      </c>
+      <c r="D86">
+        <v>1334</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0.00277777777777778</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="I86" s="1">
+        <v>0.00555555555555556</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="K86" t="s">
+        <v>356</v>
+      </c>
+      <c r="L86" t="s">
+        <v>357</v>
+      </c>
+      <c r="M86" s="1">
+        <v>0.0236111111111111</v>
+      </c>
+      <c r="N86">
+        <v>2</v>
+      </c>
+      <c r="O86" t="s">
+        <v>169</v>
+      </c>
+      <c r="P86" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q86" s="1">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="R86">
+        <v>1</v>
+      </c>
+      <c r="S86" t="s">
+        <v>359</v>
+      </c>
+      <c r="T86" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="U86" t="s">
+        <v>22</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD86">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF86" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG86">
+        <v>1200</v>
+      </c>
+      <c r="AH86">
+        <v>1100</v>
+      </c>
+      <c r="AI86">
+        <v>1600</v>
+      </c>
+      <c r="AJ86">
+        <v>1800</v>
+      </c>
+      <c r="AK86">
+        <v>2200</v>
+      </c>
+      <c r="AL86">
+        <v>2500</v>
+      </c>
+      <c r="AM86">
+        <v>2900</v>
+      </c>
+      <c r="AN86" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO86" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP86">
+        <v>1334</v>
+      </c>
+      <c r="AQ86">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11535"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="369">
   <si>
     <t>种类</t>
   </si>
@@ -1531,6 +1531,36 @@
   <si>
     <t xml:space="preserve">拆路径计数  多重集排列公式是 ans =(Σ因子)！ /  ∏ (因子！)
   u 和 v的最短路一定会经过gcd uv  路径就是 gcd到u 的答案乘以 gcd到v的答案                                       </t>
+  </si>
+  <si>
+    <t>sgt优化dp</t>
+  </si>
+  <si>
+    <t>dpij是前i个数字 匹配了目标b的j个数字花的最小代价   发现b目标数组是单调递增的
+发现当前ai进去 影响的是一段区间 可以 sgt维护区间加 单点修改 单点查询</t>
+  </si>
+  <si>
+    <t>贪心01交替</t>
+  </si>
+  <si>
+    <t xml:space="preserve">打表 </t>
+  </si>
+  <si>
+    <t>打出给出两个数字的循环节后O1做</t>
+  </si>
+  <si>
+    <t>单调性可以二分
+按从大到小贪心放每个集合 每次放的时候check不合法性就行</t>
+  </si>
+  <si>
+    <t>组合数学球盒问题/第二类斯特林数</t>
+  </si>
+  <si>
+    <t>考虑假设满足条件得每一行都有一辆车子  列的话也一样类似最后*2
+攻击对数k = n - 非空列的数量 -&gt; m= n-k          
+球盒问题 球编号不一样 因为行号不一样 盒子编号也不一样 列不一样
+现在是选n-k个盒子放n个球 都要非空 假设有一个空的 减去这种情况
+二项式反演 容斥     最后这个数量得乘以C（n，m）因为最开始定下的行没有被钦定</t>
   </si>
 </sst>
 </file>
@@ -2523,7 +2553,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ86"/>
+  <dimension ref="A1:AQ87"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="62.5714285714286" customWidth="1"/>
@@ -9729,7 +9759,7 @@
       <c r="S86" t="s">
         <v>359</v>
       </c>
-      <c r="T86" s="9" t="s">
+      <c r="T86" s="3" t="s">
         <v>360</v>
       </c>
       <c r="U86" t="s">
@@ -9738,6 +9768,12 @@
       <c r="V86">
         <v>0</v>
       </c>
+      <c r="W86" t="s">
+        <v>361</v>
+      </c>
+      <c r="X86" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="Y86" t="s">
         <v>22</v>
       </c>
@@ -9788,6 +9824,125 @@
       </c>
       <c r="AQ86">
         <v>85</v>
+      </c>
+    </row>
+    <row r="87" ht="75" spans="2:43">
+      <c r="B87">
+        <v>86</v>
+      </c>
+      <c r="D87">
+        <v>1342</v>
+      </c>
+      <c r="F87" s="1">
+        <v>0.00347222222222222</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
+        <v>363</v>
+      </c>
+      <c r="I87" s="1">
+        <v>0.0111111111111111</v>
+      </c>
+      <c r="J87">
+        <v>1</v>
+      </c>
+      <c r="K87" t="s">
+        <v>364</v>
+      </c>
+      <c r="L87" t="s">
+        <v>365</v>
+      </c>
+      <c r="M87" s="1">
+        <v>0.0236111111111111</v>
+      </c>
+      <c r="N87">
+        <v>2</v>
+      </c>
+      <c r="O87" t="s">
+        <v>251</v>
+      </c>
+      <c r="P87" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q87" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="R87">
+        <v>2</v>
+      </c>
+      <c r="S87" t="s">
+        <v>367</v>
+      </c>
+      <c r="T87" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="U87" t="s">
+        <v>22</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB87" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC87" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD87" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE87" t="s">
+        <v>316</v>
+      </c>
+      <c r="AF87" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG87">
+        <v>1000</v>
+      </c>
+      <c r="AH87">
+        <v>1100</v>
+      </c>
+      <c r="AI87">
+        <v>1600</v>
+      </c>
+      <c r="AJ87">
+        <v>1900</v>
+      </c>
+      <c r="AK87">
+        <v>2300</v>
+      </c>
+      <c r="AL87">
+        <v>3000</v>
+      </c>
+      <c r="AM87" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN87" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO87" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP87">
+        <v>1342</v>
+      </c>
+      <c r="AQ87">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="389">
   <si>
     <t>种类</t>
   </si>
@@ -1517,6 +1517,12 @@
     <t xml:space="preserve">拆位 + DP </t>
   </si>
   <si>
+    <t>拆位后 对于每一位单独考虑 用差分去做哪些区间必须都是0 ，limi=j 代表对于当前位置的 上一个0的极限位置是 j ，所以lim[R[i] + 1] = max(lim[R[i] + 1], L[i]);
+把lim给预处理一下 单调不减的是 dpi 代表当前位置作为最后一个位置填0的合法数量 钦定0和n+1位置都是0，这样dp0=0，取dpn+1的值即可
+考虑维护一个pre前缀和 前缀和存的是之前的合法位置的和 由于当前位置的0可以由之前全部合法位置直接转移过来 就是中间都是1 就左右俩位置是0
+然后限制就用双指针维护 while(l &lt; lim[i])pre -= dp[l];l += 1; 删掉不合法的即可</t>
+  </si>
+  <si>
     <t>贪心 + 双指针</t>
   </si>
   <si>
@@ -1561,6 +1567,66 @@
 球盒问题 球编号不一样 因为行号不一样 盒子编号也不一样 列不一样
 现在是选n-k个盒子放n个球 都要非空 假设有一个空的 减去这种情况
 二项式反演 容斥     最后这个数量得乘以C（n，m）因为最开始定下的行没有被钦定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET存编号 贪心二分即可 </t>
+  </si>
+  <si>
+    <t>高中数学+猜结论</t>
+  </si>
+  <si>
+    <t>树状数组+二分</t>
+  </si>
+  <si>
+    <t>这题卡线段树MLE49</t>
+  </si>
+  <si>
+    <t>二分图染色+DP</t>
+  </si>
+  <si>
+    <t>1能连2  2能连1，3   3能连1，本质上就是两种颜色 
+对森林跑一下二分图 存一下两种点的数量 后面做背包可达性DP即可 
+dpij 前i个能到达j的可达性</t>
+  </si>
+  <si>
+    <t>费用流/DP</t>
+  </si>
+  <si>
+    <t>贪心思考 ，肯定是前面放k-1个 然后对于剩下的一个位置一直重复放置删除的过程 ，二分图左边是这些士兵，右边是每种位置贡献代价</t>
+  </si>
+  <si>
+    <t>二分+ 交互+概率</t>
+  </si>
+  <si>
+    <t>C1，C2，D，E，G</t>
+  </si>
+  <si>
+    <t>C1，C2，G</t>
+  </si>
+  <si>
+    <t>1400+2000</t>
+  </si>
+  <si>
+    <t>三分/二分/枚举</t>
+  </si>
+  <si>
+    <t>被卡精度了 开longdouble就过了</t>
+  </si>
+  <si>
+    <t>枚举二分/笛卡尔树DP</t>
+  </si>
+  <si>
+    <t>值域就30，随便枚举二分维护前缀和就行</t>
+  </si>
+  <si>
+    <t>枚举+简单组合数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对于每一个数字i作为第一个数字 后面得数字都是i得倍数 且不相等 
+这样就满足题目要求得条件 后面k-1个数字能取到 n/i - 1个数字 </t>
+  </si>
+  <si>
+    <t>扫描线+计算几何</t>
   </si>
 </sst>
 </file>
@@ -2553,11 +2619,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ87"/>
+  <dimension ref="A1:AQ89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="62.5714285714286" customWidth="1"/>
-    <col min="11" max="11" width="15.247619047619" customWidth="1"/>
+    <col min="11" max="11" width="21.4285714285714" customWidth="1"/>
     <col min="12" max="12" width="39.5047619047619" customWidth="1"/>
     <col min="13" max="13" width="10.1238095238095" customWidth="1"/>
     <col min="15" max="15" width="25.6285714285714" customWidth="1"/>
@@ -2571,7 +2637,8 @@
     <col min="27" max="27" width="34.1238095238095" customWidth="1"/>
     <col min="28" max="28" width="48.1428571428571" customWidth="1"/>
     <col min="30" max="30" width="7.75238095238095" customWidth="1"/>
-    <col min="31" max="31" width="10.1238095238095" customWidth="1"/>
+    <col min="31" max="31" width="18.7142857142857" customWidth="1"/>
+    <col min="32" max="32" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42">
@@ -9591,7 +9658,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="2:43">
+    <row r="85" ht="60" spans="2:43">
       <c r="B85">
         <v>84</v>
       </c>
@@ -9652,8 +9719,8 @@
       <c r="W85" t="s">
         <v>355</v>
       </c>
-      <c r="X85" t="s">
-        <v>309</v>
+      <c r="X85" s="3" t="s">
+        <v>356</v>
       </c>
       <c r="Y85" t="s">
         <v>22</v>
@@ -9677,7 +9744,7 @@
         <v>137</v>
       </c>
       <c r="AF85" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="AG85">
         <v>1100</v>
@@ -9733,10 +9800,10 @@
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L86" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M86" s="1">
         <v>0.0236111111111111</v>
@@ -9748,7 +9815,7 @@
         <v>169</v>
       </c>
       <c r="P86" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q86" s="1">
         <v>0.0416666666666667</v>
@@ -9757,10 +9824,10 @@
         <v>1</v>
       </c>
       <c r="S86" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="T86" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U86" t="s">
         <v>22</v>
@@ -9769,10 +9836,10 @@
         <v>0</v>
       </c>
       <c r="W86" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="X86" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Y86" t="s">
         <v>22</v>
@@ -9840,7 +9907,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I87" s="1">
         <v>0.0111111111111111</v>
@@ -9849,10 +9916,10 @@
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L87" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M87" s="1">
         <v>0.0236111111111111</v>
@@ -9863,8 +9930,8 @@
       <c r="O87" t="s">
         <v>251</v>
       </c>
-      <c r="P87" s="9" t="s">
-        <v>366</v>
+      <c r="P87" s="3" t="s">
+        <v>367</v>
       </c>
       <c r="Q87" s="1">
         <v>0.05</v>
@@ -9873,10 +9940,10 @@
         <v>2</v>
       </c>
       <c r="S87" t="s">
-        <v>367</v>
-      </c>
-      <c r="T87" s="9" t="s">
         <v>368</v>
+      </c>
+      <c r="T87" s="3" t="s">
+        <v>369</v>
       </c>
       <c r="U87" t="s">
         <v>22</v>
@@ -9943,6 +10010,247 @@
       </c>
       <c r="AQ87">
         <v>86</v>
+      </c>
+    </row>
+    <row r="88" ht="45" spans="2:43">
+      <c r="B88">
+        <v>87</v>
+      </c>
+      <c r="D88">
+        <v>1354</v>
+      </c>
+      <c r="F88" s="1">
+        <v>0.00486111111111111</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88" t="s">
+        <v>370</v>
+      </c>
+      <c r="I88" s="1">
+        <v>0.0159722222222222</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88" t="s">
+        <v>371</v>
+      </c>
+      <c r="M88" t="s">
+        <v>22</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88" t="s">
+        <v>372</v>
+      </c>
+      <c r="P88" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>22</v>
+      </c>
+      <c r="R88">
+        <v>-3</v>
+      </c>
+      <c r="S88" t="s">
+        <v>374</v>
+      </c>
+      <c r="T88" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="U88" t="s">
+        <v>22</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88" t="s">
+        <v>376</v>
+      </c>
+      <c r="X88" t="s">
+        <v>377</v>
+      </c>
+      <c r="Y88" s="1">
+        <v>0.0819444444444444</v>
+      </c>
+      <c r="Z88">
+        <v>1</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>378</v>
+      </c>
+      <c r="AB88" t="s">
+        <v>309</v>
+      </c>
+      <c r="AC88" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD88">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="s">
+        <v>379</v>
+      </c>
+      <c r="AF88" t="s">
+        <v>380</v>
+      </c>
+      <c r="AG88">
+        <v>900</v>
+      </c>
+      <c r="AH88">
+        <v>1200</v>
+      </c>
+      <c r="AI88" t="s">
+        <v>381</v>
+      </c>
+      <c r="AJ88">
+        <v>1900</v>
+      </c>
+      <c r="AK88">
+        <v>2100</v>
+      </c>
+      <c r="AL88">
+        <v>2500</v>
+      </c>
+      <c r="AM88">
+        <v>2600</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO88" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP88">
+        <v>1354</v>
+      </c>
+      <c r="AQ88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" ht="30" spans="2:43">
+      <c r="B89">
+        <v>88</v>
+      </c>
+      <c r="D89">
+        <v>1359</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0.00694444444444444</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
+        <v>83</v>
+      </c>
+      <c r="I89" s="1">
+        <v>0.0111111111111111</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="K89" t="s">
+        <v>382</v>
+      </c>
+      <c r="L89" t="s">
+        <v>383</v>
+      </c>
+      <c r="M89" t="s">
+        <v>22</v>
+      </c>
+      <c r="N89">
+        <v>-4</v>
+      </c>
+      <c r="O89" t="s">
+        <v>384</v>
+      </c>
+      <c r="P89" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q89" s="1">
+        <v>0.0729166666666667</v>
+      </c>
+      <c r="R89">
+        <v>2</v>
+      </c>
+      <c r="S89" t="s">
+        <v>386</v>
+      </c>
+      <c r="T89" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="U89" t="s">
+        <v>22</v>
+      </c>
+      <c r="V89">
+        <v>-1</v>
+      </c>
+      <c r="W89" t="s">
+        <v>388</v>
+      </c>
+      <c r="X89" t="s">
+        <v>309</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB89" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC89" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD89" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE89" t="s">
+        <v>238</v>
+      </c>
+      <c r="AF89" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG89">
+        <v>1000</v>
+      </c>
+      <c r="AH89">
+        <v>1000</v>
+      </c>
+      <c r="AI89">
+        <v>1700</v>
+      </c>
+      <c r="AJ89">
+        <v>2000</v>
+      </c>
+      <c r="AK89">
+        <v>2000</v>
+      </c>
+      <c r="AL89">
+        <v>2900</v>
+      </c>
+      <c r="AM89" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN89" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO89" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP89">
+        <v>1359</v>
+      </c>
+      <c r="AQ89">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11535"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="410">
   <si>
     <t>种类</t>
   </si>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">并查集 </t>
   </si>
   <si>
-    <t>SGT分治会被卡TLE
+    <t>SGT分治会被卡MLE
 考虑对每种颜色考虑 因为并查集合并每种颜色单独考虑就行 按时间存有的数字 当前有一个颜色的格子 就先+1 看左右有没有合并好的 与周围通后要减去1
   由于颜色编号只会增大具有单调性   由此 正着做的时候 直接按这样做就行  删去的颜色怎么考虑 按时间倒着考虑即可 因为颜色也有单调性 与前面相反就行</t>
   </si>
@@ -1627,6 +1627,79 @@
   </si>
   <si>
     <t>扫描线+计算几何</t>
+  </si>
+  <si>
+    <t>二分/贪心</t>
+  </si>
+  <si>
+    <t>最小质因子得最高次数 和 n除以这个数字得和 不可能会被整除</t>
+  </si>
+  <si>
+    <t>贪心+观察</t>
+  </si>
+  <si>
+    <t>贪心后缀min预处理 每一段都是隔开得 分开乘法原理即可</t>
+  </si>
+  <si>
+    <t>计算几何+DP</t>
+  </si>
+  <si>
+    <t>走了i步当前在j得最大路径
+建立y=kx+b  当前已经在now最优 花费了n 所以最后得函数就是y=w*x+(now-w*n)
+n方枚举当前是否在某段时间是最优的 当前时间往中间缩即可 如果出现一样的时候 只取大的编号的 否则会出现一个时间多个最优 算重复</t>
+  </si>
+  <si>
+    <t>预处理+DP</t>
+  </si>
+  <si>
+    <t>n方预处理点.号的匹配上一个的情况
+分几种情况
+直接删掉当前s1i 或者匹配s2j的下一位，如果当前是点号 可以尝试删除s2的已匹配的一个字符，或者不管的话就是快速跳跃 前面点号是撤回 预处理的这一段</t>
+  </si>
+  <si>
+    <t>前缀和</t>
+  </si>
+  <si>
+    <t>模拟+dp</t>
+  </si>
+  <si>
+    <t>太史了</t>
+  </si>
+  <si>
+    <t>二分/模拟最大流</t>
+  </si>
+  <si>
+    <t>直接暴力跑flow会MLE 得考虑模拟最大流或者二分答案</t>
+  </si>
+  <si>
+    <t>线段树分治维护权值线段树</t>
+  </si>
+  <si>
+    <t>出现和消失可以丢到线段树分治上去
+每个棋子要贪心的走 就是一个abs(x - k) + y;//最低点
+贪心权值线段树二分查到对应的点 放置就行</t>
+  </si>
+  <si>
+    <t>猜测结论</t>
+  </si>
+  <si>
+    <t>由于是一个排列 所以每一段需要被删除的段其实是是独立的</t>
+  </si>
+  <si>
+    <t>并查集+启发式合并+SET二分</t>
+  </si>
+  <si>
+    <t>并查集维护当前是第几个集合合并
+启发式合并维持log的复杂度 观察到只有连续的数字才不会对答案有贡献 插入的时候二分即可</t>
+  </si>
+  <si>
+    <t>DDP用线段树维护矩阵复合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">先观察到 进位的情况 只有前一位是1的时候
+并且小于18 x是8 的时候有9-x种方法
+不进位的时候 当前位是x的时候 有x+1种方法
+列出转移方程 前i位处理好的时候的方程  然后发现可以用矩阵表示 </t>
   </si>
 </sst>
 </file>
@@ -2619,9 +2692,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ89"/>
+  <dimension ref="A1:AQ92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
+    <col min="5" max="5" width="12" customWidth="1"/>
     <col min="8" max="8" width="62.5714285714286" customWidth="1"/>
     <col min="11" max="11" width="21.4285714285714" customWidth="1"/>
     <col min="12" max="12" width="39.5047619047619" customWidth="1"/>
@@ -4370,9 +4444,6 @@
       <c r="AF17" t="s">
         <v>33</v>
       </c>
-      <c r="AI17">
-        <v>1500</v>
-      </c>
       <c r="AJ17">
         <v>2500</v>
       </c>
@@ -9954,6 +10025,9 @@
       <c r="W87" t="s">
         <v>196</v>
       </c>
+      <c r="X87" t="s">
+        <v>309</v>
+      </c>
       <c r="Y87" t="s">
         <v>22</v>
       </c>
@@ -10180,7 +10254,7 @@
       <c r="S89" t="s">
         <v>386</v>
       </c>
-      <c r="T89" s="9" t="s">
+      <c r="T89" s="3" t="s">
         <v>387</v>
       </c>
       <c r="U89" t="s">
@@ -10251,6 +10325,357 @@
       </c>
       <c r="AQ89">
         <v>88</v>
+      </c>
+    </row>
+    <row r="90" ht="88.5" spans="2:43">
+      <c r="B90">
+        <v>89</v>
+      </c>
+      <c r="D90">
+        <v>1366</v>
+      </c>
+      <c r="E90" t="s">
+        <v>389</v>
+      </c>
+      <c r="F90" s="1">
+        <v>0.0111111111111111</v>
+      </c>
+      <c r="G90">
+        <v>2</v>
+      </c>
+      <c r="H90" t="s">
+        <v>169</v>
+      </c>
+      <c r="I90" s="1">
+        <v>0.0243055555555556</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90" t="s">
+        <v>169</v>
+      </c>
+      <c r="M90" s="1">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
+      <c r="O90" t="s">
+        <v>360</v>
+      </c>
+      <c r="P90" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q90" s="1">
+        <v>0.0618055555555556</v>
+      </c>
+      <c r="R90">
+        <v>3</v>
+      </c>
+      <c r="S90" t="s">
+        <v>391</v>
+      </c>
+      <c r="T90" t="s">
+        <v>392</v>
+      </c>
+      <c r="U90" s="1">
+        <v>0.0708333333333333</v>
+      </c>
+      <c r="V90">
+        <v>2</v>
+      </c>
+      <c r="W90" t="s">
+        <v>393</v>
+      </c>
+      <c r="X90" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>395</v>
+      </c>
+      <c r="AB90" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC90" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD90">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF90" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG90">
+        <v>1100</v>
+      </c>
+      <c r="AH90">
+        <v>1300</v>
+      </c>
+      <c r="AI90">
+        <v>1500</v>
+      </c>
+      <c r="AJ90">
+        <v>2000</v>
+      </c>
+      <c r="AK90">
+        <v>2100</v>
+      </c>
+      <c r="AL90">
+        <v>2700</v>
+      </c>
+      <c r="AM90">
+        <v>2700</v>
+      </c>
+      <c r="AN90" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO90" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP90">
+        <v>1366</v>
+      </c>
+      <c r="AQ90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" ht="60" spans="2:43">
+      <c r="B91">
+        <v>90</v>
+      </c>
+      <c r="D91">
+        <v>1373</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0.00347222222222222</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91" t="s">
+        <v>169</v>
+      </c>
+      <c r="I91" s="1">
+        <v>0.00694444444444444</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91" t="s">
+        <v>169</v>
+      </c>
+      <c r="M91" s="1">
+        <v>0.0159722222222222</v>
+      </c>
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="O91" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q91" s="1">
+        <v>0.0291666666666667</v>
+      </c>
+      <c r="R91">
+        <v>1</v>
+      </c>
+      <c r="S91" t="s">
+        <v>398</v>
+      </c>
+      <c r="T91" t="s">
+        <v>399</v>
+      </c>
+      <c r="U91" t="s">
+        <v>22</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91" t="s">
+        <v>400</v>
+      </c>
+      <c r="X91" t="s">
+        <v>401</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z91">
+        <v>-9</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>402</v>
+      </c>
+      <c r="AB91" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD91">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="s">
+        <v>289</v>
+      </c>
+      <c r="AF91" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG91">
+        <v>1000</v>
+      </c>
+      <c r="AH91">
+        <v>900</v>
+      </c>
+      <c r="AI91">
+        <v>1300</v>
+      </c>
+      <c r="AJ91">
+        <v>1600</v>
+      </c>
+      <c r="AK91">
+        <v>2200</v>
+      </c>
+      <c r="AL91">
+        <v>2400</v>
+      </c>
+      <c r="AM91">
+        <v>2600</v>
+      </c>
+      <c r="AN91" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO91" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP91">
+        <v>1373</v>
+      </c>
+      <c r="AQ91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" ht="60" spans="2:43">
+      <c r="B92">
+        <v>91</v>
+      </c>
+      <c r="D92">
+        <v>1380</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0.00416666666666667</v>
+      </c>
+      <c r="G92">
+        <v>2</v>
+      </c>
+      <c r="H92" t="s">
+        <v>404</v>
+      </c>
+      <c r="I92" s="1">
+        <v>0.00833333333333333</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92" t="s">
+        <v>169</v>
+      </c>
+      <c r="M92" s="1">
+        <v>0.0138888888888889</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92" t="s">
+        <v>242</v>
+      </c>
+      <c r="P92" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q92" s="1">
+        <v>0.0402777777777778</v>
+      </c>
+      <c r="R92">
+        <v>2</v>
+      </c>
+      <c r="S92" t="s">
+        <v>406</v>
+      </c>
+      <c r="T92" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="U92" s="1">
+        <v>0.0631944444444444</v>
+      </c>
+      <c r="V92">
+        <v>3</v>
+      </c>
+      <c r="W92" t="s">
+        <v>408</v>
+      </c>
+      <c r="X92" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD92">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF92" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG92">
+        <v>900</v>
+      </c>
+      <c r="AH92">
+        <v>1400</v>
+      </c>
+      <c r="AI92">
+        <v>1400</v>
+      </c>
+      <c r="AJ92">
+        <v>2000</v>
+      </c>
+      <c r="AK92">
+        <v>2300</v>
+      </c>
+      <c r="AL92">
+        <v>2600</v>
+      </c>
+      <c r="AM92">
+        <v>2600</v>
+      </c>
+      <c r="AN92" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO92" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP92">
+        <v>1380</v>
+      </c>
+      <c r="AQ92">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18319\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B3BC1F-65FB-45F4-BB92-F9DA3CEE5238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11535"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="465">
   <si>
     <t>种类</t>
   </si>
@@ -694,6 +703,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>先把链全杀了</t>
@@ -703,7 +713,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -712,6 +722,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>然后考虑</t>
@@ -721,7 +732,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -730,6 +741,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>一条变</t>
@@ -739,7 +751,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -748,6 +760,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>一个点入读大于等于</t>
@@ -757,7 +770,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">2 </t>
     </r>
@@ -766,6 +779,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>一个点入读等于</t>
@@ -775,7 +789,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">1 </t>
     </r>
@@ -784,6 +798,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>删除这条边</t>
@@ -793,7 +808,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -802,6 +817,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>有可能</t>
@@ -811,7 +827,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -820,6 +836,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>没有环</t>
@@ -829,7 +846,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -838,6 +855,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>否则不可能</t>
@@ -851,6 +869,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>区间修改</t>
@@ -859,7 +878,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>+</t>
     </r>
@@ -867,6 +886,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>全局查询</t>
@@ -895,7 +915,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">dpij </t>
     </r>
@@ -903,6 +923,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>表示当前到</t>
@@ -911,7 +932,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> i </t>
     </r>
@@ -919,6 +940,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>同余j 的情况能否达成</t>
@@ -1369,6 +1391,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>已经遇到</t>
@@ -1378,7 +1401,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>cnt</t>
     </r>
@@ -1387,6 +1410,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>次目标串</t>
@@ -1396,7 +1420,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">
 cost = </t>
@@ -1406,6 +1430,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>从</t>
@@ -1415,7 +1440,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> pre </t>
     </r>
@@ -1424,6 +1449,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>补全到</t>
@@ -1433,7 +1459,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> u </t>
     </r>
@@ -1442,6 +1468,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>得情况</t>
@@ -1451,7 +1478,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">
 cost = dp[pre] + ranku u</t>
@@ -1461,6 +1488,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>在</t>
@@ -1470,7 +1498,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>pre</t>
     </r>
@@ -1479,6 +1507,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>子树里面得排名</t>
@@ -1488,7 +1517,7 @@
         <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">
 cost = dp[pre] + cnt - precnt
@@ -1701,400 +1730,297 @@
 不进位的时候 当前位是x的时候 有x+1种方法
 列出转移方程 前i位处理好的时候的方程  然后发现可以用矩阵表示 </t>
   </si>
+  <si>
+    <t>枚举往回跳几次 也可能最后一次往回跳一次 前缀max预处理即可</t>
+  </si>
+  <si>
+    <t>min写成max改半天</t>
+  </si>
+  <si>
+    <t>模型+贪心</t>
+  </si>
+  <si>
+    <t>分类讨论错完了 相离的情况直接考虑两种情况都跑一遍就行了</t>
+  </si>
+  <si>
+    <t>求解线性同余方程组数量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 &lt;= x, y &lt;= min(m, d)
+(x - 1) * d + y = (y - 1) * d + x (mod w);
+(y - x) * (d - 1) = 0 (mod w);
+g = __gcd(w, d - 1)
+(y - x) 是 w/g 的倍数
+w' = w/g
+(y - x) = i * w;
+y = i * w + x
+x &lt;= n - i * w
+up = (n - 1) / w; , x &gt;=1
+i = 1到up
+Σ (n - i * w)
+i </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sgt优化DP </t>
+  </si>
+  <si>
+    <t>维护区间+  单点修改 区间max  快速区间转移即可</t>
+  </si>
+  <si>
+    <t>换根DP，四次DFS是否过于逆天</t>
+  </si>
+  <si>
+    <t>E，G</t>
+  </si>
+  <si>
+    <t>dpijk 用了i个第一组的j个第二组的k个第三组的</t>
+  </si>
+  <si>
+    <t>线段树/SET</t>
+  </si>
+  <si>
+    <t>权值线段树维护前K大，单点加减，区间和，线段树二分
+由于这题改变量很少每次都只+1-1 可以用类似对顶堆的做法 维护k大的堆</t>
+  </si>
+  <si>
+    <t>枚举len暴力做是调和级数</t>
+  </si>
+  <si>
+    <t>线段树维护从当前位置开始的连续段的max长度，每次进行 L[nxt] / len 这么多段，线段树二分查找右端点暴力跳跃</t>
+  </si>
+  <si>
+    <t>前缀和+二分</t>
+  </si>
+  <si>
+    <t>笛卡尔树 最值分治</t>
+  </si>
+  <si>
+    <t>枚举最小的一些位置开始递归 当前是删除的情况 会划分出区间 递归的时候取min即可</t>
+  </si>
+  <si>
+    <t>维护前缀的状压DP</t>
+  </si>
+  <si>
+    <t>用 map&lt;int, int&gt; 存DP状态 ，因为状态比较少
+先用一个DIV存所有的非本身因子，当之前某段前缀的和能出现这个因子的时候，因子以上的部分都能被砍掉了
+每次看当前字母保留还是去掉，转移到nxt的DP状态</t>
+  </si>
+  <si>
+    <t>当m=0的时候，可以设置cnt i为当结尾选i个人的时候的多少人合法情况
+加上一个m的约束 就是多了容斥，全部可以  ---  一组关系不可以 + 两组关系不可以
+这里的关系可以枚举子集2^m，然后这个集合的L和R取交集∩，
+前i个位置的时候 相当于 cnti个合法的人里面选定j个人 剩余i-j个位置随便选 cnti-j个人
+sum[i][j] = sum[i - 1][j]+C(cnt[i] - j, i - j)
+答案就是 sum[R][siz] - sum[L - 1][siz] ，siz是m集合的人种类 然后是L到R这段区间都合法</t>
+  </si>
+  <si>
+    <t>线性DP</t>
+  </si>
+  <si>
+    <t>贪心找到中间最大空隙 这里的是不取的 分成左右两段即可</t>
+  </si>
+  <si>
+    <t>扫描线维护区间只出现k次</t>
+  </si>
+  <si>
+    <t>诈骗+贪心</t>
+  </si>
+  <si>
+    <t>手玩一下，发现最终就是能变成2</t>
+  </si>
+  <si>
+    <t>SET模拟+贪心</t>
+  </si>
+  <si>
+    <t>SET存哪些可以取的位置 就是不止一段的长度 这些先存SET里面，
+如果SET空了，那只能被迫删前缀也就是刚好第一个字符的了
+前缀删除维护一个前缀即可 细节略多 记得还要用vis标记每个位置状态</t>
+  </si>
+  <si>
+    <t>SGT线段树/树状数组维护区间+SET模拟</t>
+  </si>
+  <si>
+    <t>又是这题之前2025马蹄杯第一场初赛就见过原题，然后之前某场EDU我也做过一样题
+SET存字母状态 每次贪心取队首 丢到i位置 对中间的字母都有+1的贡献</t>
+  </si>
+  <si>
+    <t>状态的设置多余了这题做的时候
+考虑每次从第一个位置转移的话 设置当前为刚好能补满弹药的状态就行
+反正n方能遍历到全部情况 没法往后转移也就是当前没法补满 这个题状态设计太精妙了</t>
+  </si>
+  <si>
+    <t>flow最小割/状压子集DP</t>
+  </si>
+  <si>
+    <t>// 二分图 左边是点 右边是层数的编号
+// 最小割割的是wi点权*j层
+// bi = aui - avi &gt; 0
+// avi,j -&gt; aui,j+1 = MAX 有这个限制 不能割
+// \sum_{(u,v) \in E} w_i \cdot (a_u - a_v)
+// \sum_{(u,v) \in E} (w_i \cdot a_u - w_i \cdot a_v) =
+// \sum_{i=1}^n a_i \left( \sum_{(i,v) \in E} w_{i,v} - \sum_{(u,i) \in E} w_{u,i} \right)
+// W_i = (\sum w_{out} - \sum w_{in}) 点 i 的出边权值和减去入边权值和
+//目标函数变为 Minimize \sum_{i=1}^n a_i \cdot W_i</t>
+  </si>
+  <si>
+    <t>FLOW/DP</t>
+  </si>
+  <si>
+    <t>二分图最大匹配/
+dp[i][j]为前 i 个时刻取出了前 j 物品的花费
+dp[i][j] = min(dp[i - 1][j], dp[i - 1][j - 1] + abs(i - a[j]));</t>
+  </si>
+  <si>
+    <t>SET+贪心模拟</t>
+  </si>
+  <si>
+    <t>用SET模拟贪心最多建节点一层层往下做即可</t>
+  </si>
+  <si>
+    <t>最长上升子序列</t>
+  </si>
+  <si>
+    <t>分段做，对于被定死的位置来说，每一段都是独立的</t>
+  </si>
+  <si>
+    <t>哈希被卡常TLE了，只能AC自动机上维护回跳边的多维护一个从哪里来的数组方便转移</t>
+  </si>
+  <si>
+    <t>二分套二分/贪心</t>
+  </si>
+  <si>
+    <t>前缀和优化DP</t>
+  </si>
+  <si>
+    <t>枚举半径，因为要刚好覆盖</t>
+  </si>
+  <si>
+    <t>非VP</t>
+  </si>
+  <si>
+    <t>非VP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>G</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>三分凸包+中位数定理</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>观察到对于每一个固定的正方形的点，随着边长变大后，
+贡献是一个先减小后增大的凸包，三分凸包即可</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>字符串贪心观察+dp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>观察到 每一个i位置最多交换到i-2的位置，所以i-3的位置肯定是被固定下来的，所以
+dp0/1  维护的四个位置  i-2 i-1 i i+1 0/1代表当前位置有无和前面做交换
+dpi-3的位置就是固定下来的</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>区间重叠中间点定理</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>两个区间的中点越接近的时候 重叠面积最大
+所以把选手按中点排序后 一定存在这个最优秀分割点，预处理选手的前后缀
+枚举哪个选手是前缀的前面和哪个是后缀的加起来取max就行</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>树上博弈</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>F，G</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>淀粉质+？？？</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="Consolas"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF6A9955"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10.5"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2102,268 +2028,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2375,68 +2059,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常規" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="貨幣" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="貨幣[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超鏈接" xfId="6" builtinId="8"/>
-    <cellStyle name="已訪問的超鏈接" xfId="7" builtinId="9"/>
-    <cellStyle name="註釋" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文字" xfId="9" builtinId="11"/>
-    <cellStyle name="標題" xfId="10" builtinId="15"/>
-    <cellStyle name="解釋性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="標題 1" xfId="12" builtinId="16"/>
-    <cellStyle name="標題 2" xfId="13" builtinId="17"/>
-    <cellStyle name="標題 3" xfId="14" builtinId="18"/>
-    <cellStyle name="標題 4" xfId="15" builtinId="19"/>
-    <cellStyle name="輸入" xfId="16" builtinId="20"/>
-    <cellStyle name="輸出" xfId="17" builtinId="21"/>
-    <cellStyle name="計算" xfId="18" builtinId="22"/>
-    <cellStyle name="檢查儲存格" xfId="19" builtinId="23"/>
-    <cellStyle name="鏈接儲存格" xfId="20" builtinId="24"/>
-    <cellStyle name="匯總" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="適中" xfId="24" builtinId="28"/>
-    <cellStyle name="強調文字顏色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 強調文字顏色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 強調文字顏色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 強調文字顏色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="強調文字顏色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 強調文字顏色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 強調文字顏色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 強調文字顏色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="強調文字顏色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 強調文字顏色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 強調文字顏色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 強調文字顏色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="強調文字顏色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 強調文字顏色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 強調文字顏色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 強調文字顏色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="強調文字顏色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 強調文字顏色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 強調文字顏色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 強調文字顏色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="強調文字顏色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 強調文字顏色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 強調文字顏色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 強調文字顏色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2686,36 +2329,36 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AQ92"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AQ100"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="8" max="8" width="62.5714285714286" customWidth="1"/>
-    <col min="11" max="11" width="21.4285714285714" customWidth="1"/>
-    <col min="12" max="12" width="39.5047619047619" customWidth="1"/>
-    <col min="13" max="13" width="10.1238095238095" customWidth="1"/>
-    <col min="15" max="15" width="25.6285714285714" customWidth="1"/>
-    <col min="16" max="16" width="70.8761904761905" customWidth="1"/>
-    <col min="17" max="17" width="13.752380952381" customWidth="1"/>
-    <col min="19" max="19" width="40.1238095238095" customWidth="1"/>
-    <col min="20" max="20" width="79.7523809523809" customWidth="1"/>
-    <col min="23" max="23" width="34.8761904761905" customWidth="1"/>
-    <col min="24" max="24" width="145.371428571429" customWidth="1"/>
-    <col min="25" max="25" width="12.3714285714286" customWidth="1"/>
-    <col min="27" max="27" width="34.1238095238095" customWidth="1"/>
-    <col min="28" max="28" width="48.1428571428571" customWidth="1"/>
-    <col min="30" max="30" width="7.75238095238095" customWidth="1"/>
-    <col min="31" max="31" width="18.7142857142857" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" customWidth="1"/>
+    <col min="11" max="11" width="21.453125" customWidth="1"/>
+    <col min="12" max="12" width="54.7265625" customWidth="1"/>
+    <col min="13" max="13" width="10.08984375" customWidth="1"/>
+    <col min="15" max="15" width="25.6328125" customWidth="1"/>
+    <col min="16" max="16" width="70.90625" customWidth="1"/>
+    <col min="17" max="17" width="13.7265625" customWidth="1"/>
+    <col min="19" max="19" width="40.08984375" customWidth="1"/>
+    <col min="20" max="20" width="79.7265625" customWidth="1"/>
+    <col min="23" max="23" width="34.90625" customWidth="1"/>
+    <col min="24" max="24" width="145.36328125" customWidth="1"/>
+    <col min="25" max="25" width="12.36328125" customWidth="1"/>
+    <col min="27" max="27" width="34.08984375" customWidth="1"/>
+    <col min="28" max="28" width="83.453125" customWidth="1"/>
+    <col min="30" max="30" width="7.7265625" customWidth="1"/>
+    <col min="31" max="31" width="18.7265625" customWidth="1"/>
     <col min="32" max="32" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2843,7 +2486,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2857,13 +2500,13 @@
         <v>598</v>
       </c>
       <c r="F2" s="1">
-        <v>0.00138888888888889</v>
+        <v>1.38888888888889E-3</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="I2" s="1">
-        <v>0.0152777777777778</v>
+        <v>1.52777777777778E-2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -2879,7 +2522,7 @@
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1">
-        <v>0.0243055555555556</v>
+        <v>2.4305555555555601E-2</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -2948,7 +2591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -2959,20 +2602,20 @@
         <v>600</v>
       </c>
       <c r="F3" s="1">
-        <v>0.0125</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="I3" s="1">
-        <v>0.00277777777777778</v>
+        <v>2.7777777777777801E-3</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1">
-        <v>0.0243055555555556</v>
+        <v>2.4305555555555601E-2</v>
       </c>
       <c r="N3">
         <v>2</v>
@@ -2991,7 +2634,7 @@
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1">
-        <v>0.0381944444444444</v>
+        <v>3.8194444444444399E-2</v>
       </c>
       <c r="V3">
         <v>1</v>
@@ -3001,7 +2644,7 @@
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1">
-        <v>0.0729166666666667</v>
+        <v>7.2916666666666699E-2</v>
       </c>
       <c r="Z3">
         <v>1</v>
@@ -3049,7 +2692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3060,20 +2703,20 @@
         <v>609</v>
       </c>
       <c r="F4" s="1">
-        <v>0.00625</v>
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="I4" s="1">
-        <v>0.00972222222222222</v>
+        <v>9.7222222222222206E-3</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1">
-        <v>0.0180555555555556</v>
+        <v>1.8055555555555599E-2</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -3083,7 +2726,7 @@
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1">
-        <v>0.0645833333333333</v>
+        <v>6.4583333333333298E-2</v>
       </c>
       <c r="R4">
         <v>2</v>
@@ -3093,7 +2736,7 @@
       </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1">
-        <v>0.0458333333333333</v>
+        <v>4.5833333333333302E-2</v>
       </c>
       <c r="V4">
         <v>1</v>
@@ -3150,7 +2793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:43">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3161,27 +2804,27 @@
         <v>612</v>
       </c>
       <c r="F5" s="1">
-        <v>0.00416666666666667</v>
+        <v>4.1666666666666701E-3</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="I5" s="1">
-        <v>0.0111111111111111</v>
+        <v>1.1111111111111099E-2</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1">
-        <v>0.0222222222222222</v>
+        <v>2.2222222222222199E-2</v>
       </c>
       <c r="N5">
         <v>3</v>
       </c>
       <c r="P5" s="1"/>
       <c r="Q5" s="1">
-        <v>0.0583333333333333</v>
+        <v>5.83333333333333E-2</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -3247,7 +2890,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:43">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3258,27 +2901,27 @@
         <v>616</v>
       </c>
       <c r="F6" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="I6" s="1">
-        <v>0.00555555555555556</v>
+        <v>5.5555555555555601E-3</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1">
-        <v>0.0354166666666667</v>
+        <v>3.54166666666667E-2</v>
       </c>
       <c r="N6">
         <v>10</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1">
-        <v>0.0409722222222222</v>
+        <v>4.0972222222222202E-2</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -3288,7 +2931,7 @@
       </c>
       <c r="T6" s="1"/>
       <c r="U6" s="1">
-        <v>0.0652777777777778</v>
+        <v>6.5277777777777796E-2</v>
       </c>
       <c r="V6">
         <v>2</v>
@@ -3345,7 +2988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -3356,20 +2999,20 @@
         <v>620</v>
       </c>
       <c r="F7" s="1">
-        <v>0.000694444444444444</v>
+        <v>6.9444444444444404E-4</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1">
-        <v>0.00902777777777778</v>
+        <v>9.0277777777777804E-3</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -3379,7 +3022,7 @@
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1">
-        <v>0.08125</v>
+        <v>8.1250000000000003E-2</v>
       </c>
       <c r="R7">
         <v>2</v>
@@ -3389,7 +3032,7 @@
       </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1">
-        <v>0.05625</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="V7">
         <v>1</v>
@@ -3446,7 +3089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:43">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -3457,20 +3100,20 @@
         <v>622</v>
       </c>
       <c r="F8" s="1">
-        <v>0.00208333333333333</v>
+        <v>2.0833333333333298E-3</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="I8" s="1">
-        <v>0.00555555555555556</v>
+        <v>5.5555555555555601E-3</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1">
-        <v>0.0145833333333333</v>
+        <v>1.4583333333333301E-2</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -3548,7 +3191,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:43">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -3559,20 +3202,20 @@
         <v>628</v>
       </c>
       <c r="F9" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="I9" s="1">
-        <v>0.00694444444444444</v>
+        <v>6.9444444444444397E-3</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1">
-        <v>0.0118055555555556</v>
+        <v>1.18055555555556E-2</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -3582,7 +3225,7 @@
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1">
-        <v>0.0368055555555556</v>
+        <v>3.6805555555555598E-2</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -3651,7 +3294,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:43">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -3662,20 +3305,20 @@
         <v>632</v>
       </c>
       <c r="F10" s="1">
-        <v>0.00694444444444444</v>
+        <v>6.9444444444444397E-3</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="I10" s="1">
-        <v>0.0104166666666667</v>
+        <v>1.0416666666666701E-2</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1">
-        <v>0.0256944444444444</v>
+        <v>2.5694444444444402E-2</v>
       </c>
       <c r="N10">
         <v>2</v>
@@ -3685,7 +3328,7 @@
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1">
-        <v>0.0652777777777778</v>
+        <v>6.5277777777777796E-2</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -3754,7 +3397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:43">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3765,13 +3408,13 @@
         <v>652</v>
       </c>
       <c r="F11" s="1">
-        <v>0.00902777777777778</v>
+        <v>9.0277777777777804E-3</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>0.00833333333333333</v>
+        <v>8.3333333333333297E-3</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -3790,7 +3433,7 @@
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1">
-        <v>0.0215277777777778</v>
+        <v>2.1527777777777798E-2</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -3862,7 +3505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:43">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3873,20 +3516,20 @@
         <v>660</v>
       </c>
       <c r="F12" s="1">
-        <v>0.0131944444444444</v>
+        <v>1.3194444444444399E-2</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="I12" s="1">
-        <v>0.00972222222222222</v>
+        <v>9.7222222222222206E-3</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1">
-        <v>0.0236111111111111</v>
+        <v>2.36111111111111E-2</v>
       </c>
       <c r="N12">
         <v>2</v>
@@ -3896,7 +3539,7 @@
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1">
-        <v>0.0458333333333333</v>
+        <v>4.5833333333333302E-2</v>
       </c>
       <c r="R12">
         <v>2</v>
@@ -3962,7 +3605,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:43">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -3973,27 +3616,27 @@
         <v>665</v>
       </c>
       <c r="F13" s="1">
-        <v>0.0229166666666667</v>
+        <v>2.29166666666667E-2</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="I13" s="1">
-        <v>0.00763888888888889</v>
+        <v>7.6388888888888904E-3</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1">
-        <v>0.0131944444444444</v>
+        <v>1.3194444444444399E-2</v>
       </c>
       <c r="N13">
         <v>1</v>
       </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1">
-        <v>0.0319444444444444</v>
+        <v>3.19444444444444E-2</v>
       </c>
       <c r="R13">
         <v>2</v>
@@ -4003,7 +3646,7 @@
       </c>
       <c r="T13" s="1"/>
       <c r="U13" s="1">
-        <v>0.0673611111111111</v>
+        <v>6.7361111111111094E-2</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -4063,7 +3706,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:43">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -4074,20 +3717,20 @@
         <v>678</v>
       </c>
       <c r="F14" s="1">
-        <v>0.000694444444444444</v>
+        <v>6.9444444444444404E-4</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="I14" s="1">
-        <v>0.00763888888888889</v>
+        <v>7.6388888888888904E-3</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1">
-        <v>0.00972222222222222</v>
+        <v>9.7222222222222206E-3</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -4097,7 +3740,7 @@
       </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1">
-        <v>0.0277777777777778</v>
+        <v>2.7777777777777801E-2</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -4166,7 +3809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:43">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -4177,27 +3820,27 @@
         <v>691</v>
       </c>
       <c r="F15" s="1">
-        <v>0.00138888888888889</v>
+        <v>1.38888888888889E-3</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="I15" s="1">
-        <v>0.0180555555555556</v>
+        <v>1.8055555555555599E-2</v>
       </c>
       <c r="J15">
         <v>4</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1">
-        <v>0.0375</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="N15">
         <v>2</v>
       </c>
       <c r="P15" s="1"/>
       <c r="Q15" s="1">
-        <v>0.0430555555555556</v>
+        <v>4.3055555555555597E-2</v>
       </c>
       <c r="R15">
         <v>2</v>
@@ -4266,7 +3909,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:43">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -4277,27 +3920,27 @@
         <v>702</v>
       </c>
       <c r="F16" s="1">
-        <v>0.00555555555555556</v>
+        <v>5.5555555555555601E-3</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="I16" s="1">
-        <v>0.00972222222222222</v>
+        <v>9.7222222222222206E-3</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1">
-        <v>0.0201388888888889</v>
+        <v>2.0138888888888901E-2</v>
       </c>
       <c r="N16">
         <v>1</v>
       </c>
       <c r="P16" s="1"/>
       <c r="Q16" s="1">
-        <v>0.0263888888888889</v>
+        <v>2.6388888888888899E-2</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -4364,7 +4007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:43">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -4375,13 +4018,13 @@
         <v>710</v>
       </c>
       <c r="F17" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="I17" s="1">
-        <v>0.00486111111111111</v>
+        <v>4.8611111111111103E-3</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -4391,7 +4034,7 @@
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1">
-        <v>0.0611111111111111</v>
+        <v>6.1111111111111102E-2</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -4469,7 +4112,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:43">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -4480,13 +4123,13 @@
         <v>762</v>
       </c>
       <c r="F18" s="1">
-        <v>0.00555555555555556</v>
+        <v>5.5555555555555601E-3</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="I18" s="1">
-        <v>0.0104166666666667</v>
+        <v>1.0416666666666701E-2</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -4576,7 +4219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:43">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -4587,13 +4230,13 @@
         <v>792</v>
       </c>
       <c r="F19" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="I19" s="1">
-        <v>0.00972222222222222</v>
+        <v>9.7222222222222206E-3</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -4603,7 +4246,7 @@
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1">
-        <v>0.0243055555555556</v>
+        <v>2.4305555555555601E-2</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -4613,7 +4256,7 @@
       </c>
       <c r="P19" s="1"/>
       <c r="Q19" s="1">
-        <v>0.0826388888888889</v>
+        <v>8.2638888888888901E-2</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -4685,7 +4328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" ht="15.75" spans="1:43">
+    <row r="20" spans="1:43" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -4696,13 +4339,13 @@
         <v>797</v>
       </c>
       <c r="F20" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="I20" s="1">
-        <v>0.00694444444444444</v>
+        <v>6.9444444444444397E-3</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -4724,7 +4367,7 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1">
-        <v>0.0284722222222222</v>
+        <v>2.8472222222222201E-2</v>
       </c>
       <c r="R20">
         <v>2</v>
@@ -4734,7 +4377,7 @@
       </c>
       <c r="T20" s="1"/>
       <c r="U20" s="1">
-        <v>0.0326388888888889</v>
+        <v>3.2638888888888898E-2</v>
       </c>
       <c r="V20">
         <v>1</v>
@@ -4751,7 +4394,7 @@
       <c r="Z20">
         <v>-5</v>
       </c>
-      <c r="AA20" s="8" t="s">
+      <c r="AA20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AB20" t="s">
@@ -4797,7 +4440,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:43">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -4808,13 +4451,13 @@
         <v>803</v>
       </c>
       <c r="F21" s="1">
-        <v>0.00416666666666667</v>
+        <v>4.1666666666666701E-3</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="I21" s="1">
-        <v>0.00763888888888889</v>
+        <v>7.6388888888888904E-3</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -4822,11 +4465,11 @@
       <c r="K21" t="s">
         <v>94</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="L21" s="3" t="s">
         <v>95</v>
       </c>
       <c r="M21" s="1">
-        <v>0.0215277777777778</v>
+        <v>2.1527777777777798E-2</v>
       </c>
       <c r="N21">
         <v>3</v>
@@ -4835,7 +4478,7 @@
         <v>30</v>
       </c>
       <c r="Q21" s="1">
-        <v>0.0368055555555556</v>
+        <v>3.6805555555555598E-2</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -4856,7 +4499,7 @@
         <v>98</v>
       </c>
       <c r="Y21" s="1">
-        <v>0.0777777777777778</v>
+        <v>7.7777777777777807E-2</v>
       </c>
       <c r="Z21">
         <v>1</v>
@@ -4907,7 +4550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:43">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -4918,13 +4561,13 @@
         <v>808</v>
       </c>
       <c r="F22" s="1">
-        <v>0.00625</v>
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="I22" s="1">
-        <v>0.00972222222222222</v>
+        <v>9.7222222222222206E-3</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -4933,7 +4576,7 @@
         <v>102</v>
       </c>
       <c r="M22" s="1">
-        <v>0.0145833333333333</v>
+        <v>1.4583333333333301E-2</v>
       </c>
       <c r="N22">
         <v>1</v>
@@ -4942,7 +4585,7 @@
         <v>103</v>
       </c>
       <c r="Q22" s="1">
-        <v>0.0270833333333333</v>
+        <v>2.70833333333333E-2</v>
       </c>
       <c r="R22">
         <v>3</v>
@@ -4951,7 +4594,7 @@
         <v>104</v>
       </c>
       <c r="U22" s="1">
-        <v>0.0423611111111111</v>
+        <v>4.2361111111111099E-2</v>
       </c>
       <c r="V22">
         <v>3</v>
@@ -4960,7 +4603,7 @@
         <v>105</v>
       </c>
       <c r="Y22" s="1">
-        <v>0.0597222222222222</v>
+        <v>5.9722222222222197E-2</v>
       </c>
       <c r="Z22">
         <v>3</v>
@@ -5011,7 +4654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:43">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -5022,7 +4665,7 @@
         <v>813</v>
       </c>
       <c r="F23" s="1">
-        <v>0.00208333333333333</v>
+        <v>2.0833333333333298E-3</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -5031,7 +4674,7 @@
         <v>108</v>
       </c>
       <c r="I23" s="1">
-        <v>0.00972222222222222</v>
+        <v>9.7222222222222206E-3</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -5040,7 +4683,7 @@
         <v>109</v>
       </c>
       <c r="M23" s="1">
-        <v>0.0340277777777778</v>
+        <v>3.4027777777777803E-2</v>
       </c>
       <c r="N23">
         <v>3</v>
@@ -5076,7 +4719,7 @@
         <v>115</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.0729166666666667</v>
+        <v>7.2916666666666699E-2</v>
       </c>
       <c r="Z23">
         <v>1</v>
@@ -5130,7 +4773,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:43">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -5141,13 +4784,13 @@
         <v>817</v>
       </c>
       <c r="F24" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="I24" s="1">
-        <v>0.00833333333333333</v>
+        <v>8.3333333333333297E-3</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -5156,7 +4799,7 @@
         <v>108</v>
       </c>
       <c r="M24" s="1">
-        <v>0.0118055555555556</v>
+        <v>1.18055555555556E-2</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -5180,7 +4823,7 @@
         <v>120</v>
       </c>
       <c r="U24" s="1">
-        <v>0.0347222222222222</v>
+        <v>3.4722222222222203E-2</v>
       </c>
       <c r="V24">
         <v>1</v>
@@ -5192,7 +4835,7 @@
         <v>122</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.0854166666666667</v>
+        <v>8.5416666666666696E-2</v>
       </c>
       <c r="Z24">
         <v>3</v>
@@ -5246,7 +4889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:43">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -5257,7 +4900,7 @@
         <v>818</v>
       </c>
       <c r="F25" s="1">
-        <v>0.00208333333333333</v>
+        <v>2.0833333333333298E-3</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -5266,7 +4909,7 @@
         <v>123</v>
       </c>
       <c r="I25" s="1">
-        <v>0.0125</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -5278,7 +4921,7 @@
         <v>124</v>
       </c>
       <c r="M25" s="1">
-        <v>0.05625</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -5290,7 +4933,7 @@
         <v>126</v>
       </c>
       <c r="Q25" s="1">
-        <v>0.0861111111111111</v>
+        <v>8.6111111111111097E-2</v>
       </c>
       <c r="R25">
         <v>3</v>
@@ -5323,7 +4966,7 @@
         <v>131</v>
       </c>
       <c r="AC25" s="1">
-        <v>0.0784722222222222</v>
+        <v>7.8472222222222193E-2</v>
       </c>
       <c r="AD25">
         <v>1</v>
@@ -5365,7 +5008,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:43">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -5376,25 +5019,25 @@
         <v>825</v>
       </c>
       <c r="F26" s="1">
-        <v>0.00486111111111111</v>
+        <v>4.8611111111111103E-3</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="I26" s="1">
-        <v>0.00972222222222222</v>
+        <v>9.7222222222222206E-3</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="M26" s="1">
-        <v>0.0159722222222222</v>
+        <v>1.59722222222222E-2</v>
       </c>
       <c r="N26">
         <v>2</v>
       </c>
       <c r="Q26" s="1">
-        <v>0.0256944444444444</v>
+        <v>2.5694444444444402E-2</v>
       </c>
       <c r="R26">
         <v>2</v>
@@ -5406,7 +5049,7 @@
         <v>133</v>
       </c>
       <c r="U26" s="1">
-        <v>0.0729166666666667</v>
+        <v>7.2916666666666699E-2</v>
       </c>
       <c r="V26">
         <v>4</v>
@@ -5469,7 +5112,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:43">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -5480,19 +5123,19 @@
         <v>837</v>
       </c>
       <c r="F27" s="1">
-        <v>0.00277777777777778</v>
+        <v>2.7777777777777801E-3</v>
       </c>
       <c r="G27">
         <v>2</v>
       </c>
       <c r="I27" s="1">
-        <v>0.00902777777777778</v>
+        <v>9.0277777777777804E-3</v>
       </c>
       <c r="J27">
         <v>1</v>
       </c>
       <c r="M27" s="1">
-        <v>0.0166666666666667</v>
+        <v>1.6666666666666701E-2</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -5504,7 +5147,7 @@
         <v>139</v>
       </c>
       <c r="Q27" s="1">
-        <v>0.0777777777777778</v>
+        <v>7.7777777777777807E-2</v>
       </c>
       <c r="R27">
         <v>8</v>
@@ -5579,7 +5222,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:43">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -5590,25 +5233,25 @@
         <v>845</v>
       </c>
       <c r="F28" s="1">
-        <v>0.00208333333333333</v>
+        <v>2.0833333333333298E-3</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="I28" s="1">
-        <v>0.00486111111111111</v>
+        <v>4.8611111111111103E-3</v>
       </c>
       <c r="J28">
         <v>1</v>
       </c>
       <c r="M28" s="1">
-        <v>0.00833333333333333</v>
+        <v>8.3333333333333297E-3</v>
       </c>
       <c r="N28">
         <v>1</v>
       </c>
       <c r="Q28" s="1">
-        <v>0.0208333333333333</v>
+        <v>2.0833333333333301E-2</v>
       </c>
       <c r="R28">
         <v>2</v>
@@ -5641,7 +5284,7 @@
         <v>148</v>
       </c>
       <c r="AC28" s="1">
-        <v>0.0284722222222222</v>
+        <v>2.8472222222222201E-2</v>
       </c>
       <c r="AD28">
         <v>1</v>
@@ -5683,7 +5326,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:43">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -5694,7 +5337,7 @@
         <v>846</v>
       </c>
       <c r="F29" s="1">
-        <v>0.00208333333333333</v>
+        <v>2.0833333333333298E-3</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5703,7 +5346,7 @@
         <v>149</v>
       </c>
       <c r="I29" s="1">
-        <v>0.0326388888888889</v>
+        <v>3.2638888888888898E-2</v>
       </c>
       <c r="J29">
         <v>2</v>
@@ -5712,7 +5355,7 @@
         <v>150</v>
       </c>
       <c r="M29" s="1">
-        <v>0.0395833333333333</v>
+        <v>3.9583333333333297E-2</v>
       </c>
       <c r="N29">
         <v>1</v>
@@ -5721,7 +5364,7 @@
         <v>151</v>
       </c>
       <c r="Q29" s="1">
-        <v>0.0472222222222222</v>
+        <v>4.72222222222222E-2</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -5799,7 +5442,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:43">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -5810,13 +5453,13 @@
         <v>863</v>
       </c>
       <c r="F30" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="I30" s="1">
-        <v>0.00833333333333333</v>
+        <v>8.3333333333333297E-3</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -5828,7 +5471,7 @@
         <v>157</v>
       </c>
       <c r="M30" s="1">
-        <v>0.0208333333333333</v>
+        <v>2.0833333333333301E-2</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -5837,7 +5480,7 @@
         <v>158</v>
       </c>
       <c r="Q30" s="1">
-        <v>0.0618055555555556</v>
+        <v>6.18055555555556E-2</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -5849,7 +5492,7 @@
         <v>160</v>
       </c>
       <c r="U30" s="1">
-        <v>0.0375</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="V30">
         <v>2</v>
@@ -5861,7 +5504,7 @@
         <v>161</v>
       </c>
       <c r="Y30" s="1">
-        <v>0.0798611111111111</v>
+        <v>7.9861111111111105E-2</v>
       </c>
       <c r="Z30">
         <v>1</v>
@@ -5912,7 +5555,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:43">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -5923,19 +5566,19 @@
         <v>873</v>
       </c>
       <c r="F31" s="1">
-        <v>0.00138888888888889</v>
+        <v>1.38888888888889E-3</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="I31" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="M31" s="1">
-        <v>0.0118055555555556</v>
+        <v>1.18055555555556E-2</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -5959,7 +5602,7 @@
         <v>166</v>
       </c>
       <c r="U31" s="1">
-        <v>0.0590277777777778</v>
+        <v>5.9027777777777797E-2</v>
       </c>
       <c r="V31">
         <v>2</v>
@@ -6022,7 +5665,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:43">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -6033,13 +5676,13 @@
         <v>884</v>
       </c>
       <c r="F32" s="1">
-        <v>0.000694444444444444</v>
+        <v>6.9444444444444404E-4</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="I32" s="1">
-        <v>0.00416666666666667</v>
+        <v>4.1666666666666701E-3</v>
       </c>
       <c r="J32">
         <v>2</v>
@@ -6051,7 +5694,7 @@
         <v>169</v>
       </c>
       <c r="M32" s="1">
-        <v>0.00833333333333333</v>
+        <v>8.3333333333333297E-3</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -6141,7 +5784,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" ht="210" spans="1:43">
+    <row r="33" spans="1:43" ht="196" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -6152,13 +5795,13 @@
         <v>888</v>
       </c>
       <c r="F33" s="1">
-        <v>0.000694444444444444</v>
+        <v>6.9444444444444404E-4</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="I33" s="1">
-        <v>0.00208333333333333</v>
+        <v>2.0833333333333298E-3</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -6167,7 +5810,7 @@
         <v>83</v>
       </c>
       <c r="M33" s="1">
-        <v>0.00763888888888889</v>
+        <v>7.6388888888888904E-3</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -6175,11 +5818,11 @@
       <c r="O33" t="s">
         <v>177</v>
       </c>
-      <c r="P33" s="3" t="s">
+      <c r="P33" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Q33" s="1">
-        <v>0.0465277777777778</v>
+        <v>4.65277777777778E-2</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -6191,7 +5834,7 @@
         <v>180</v>
       </c>
       <c r="U33" s="1">
-        <v>0.0194444444444444</v>
+        <v>1.94444444444444E-2</v>
       </c>
       <c r="V33">
         <v>1</v>
@@ -6199,7 +5842,7 @@
       <c r="W33" t="s">
         <v>181</v>
       </c>
-      <c r="X33" s="3" t="s">
+      <c r="X33" s="4" t="s">
         <v>182</v>
       </c>
       <c r="Y33" t="s">
@@ -6211,11 +5854,11 @@
       <c r="AA33" t="s">
         <v>183</v>
       </c>
-      <c r="AB33" s="3" t="s">
+      <c r="AB33" s="4" t="s">
         <v>184</v>
       </c>
       <c r="AC33" s="1">
-        <v>0.03125</v>
+        <v>3.125E-2</v>
       </c>
       <c r="AD33">
         <v>1</v>
@@ -6257,7 +5900,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:43">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -6268,7 +5911,7 @@
         <v>893</v>
       </c>
       <c r="F34" s="1">
-        <v>0.00486111111111111</v>
+        <v>4.8611111111111103E-3</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -6277,7 +5920,7 @@
         <v>83</v>
       </c>
       <c r="I34" s="1">
-        <v>0.0131944444444444</v>
+        <v>1.3194444444444399E-2</v>
       </c>
       <c r="J34">
         <v>3</v>
@@ -6286,7 +5929,7 @@
         <v>185</v>
       </c>
       <c r="M34" s="1">
-        <v>0.0159722222222222</v>
+        <v>1.59722222222222E-2</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -6298,7 +5941,7 @@
         <v>187</v>
       </c>
       <c r="Q34" s="1">
-        <v>0.0326388888888889</v>
+        <v>3.2638888888888898E-2</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -6319,7 +5962,7 @@
         <v>190</v>
       </c>
       <c r="Y34" s="1">
-        <v>0.0506944444444444</v>
+        <v>5.0694444444444403E-2</v>
       </c>
       <c r="Z34">
         <v>1</v>
@@ -6373,7 +6016,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" ht="76.5" spans="1:43">
+    <row r="35" spans="1:43" ht="81" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -6384,7 +6027,7 @@
         <v>903</v>
       </c>
       <c r="F35" s="1">
-        <v>0.00138888888888889</v>
+        <v>1.38888888888889E-3</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -6393,7 +6036,7 @@
         <v>83</v>
       </c>
       <c r="I35" s="1">
-        <v>0.00694444444444444</v>
+        <v>6.9444444444444397E-3</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -6402,7 +6045,7 @@
         <v>191</v>
       </c>
       <c r="M35" s="1">
-        <v>0.0125</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="N35">
         <v>2</v>
@@ -6414,7 +6057,7 @@
         <v>193</v>
       </c>
       <c r="Q35" s="1">
-        <v>0.0236111111111111</v>
+        <v>2.36111111111111E-2</v>
       </c>
       <c r="R35">
         <v>2</v>
@@ -6422,7 +6065,7 @@
       <c r="S35" t="s">
         <v>194</v>
       </c>
-      <c r="T35" s="4" t="s">
+      <c r="T35" s="5" t="s">
         <v>195</v>
       </c>
       <c r="U35" t="s">
@@ -6486,7 +6129,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" ht="45" spans="1:43">
+    <row r="36" spans="1:43" ht="42" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -6497,7 +6140,7 @@
         <v>911</v>
       </c>
       <c r="F36" s="1">
-        <v>0.0104166666666667</v>
+        <v>1.0416666666666701E-2</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6506,7 +6149,7 @@
         <v>198</v>
       </c>
       <c r="I36" s="1">
-        <v>0.0138888888888889</v>
+        <v>1.38888888888889E-2</v>
       </c>
       <c r="J36">
         <v>2</v>
@@ -6515,7 +6158,7 @@
         <v>199</v>
       </c>
       <c r="M36" s="1">
-        <v>0.0201388888888889</v>
+        <v>2.0138888888888901E-2</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -6523,7 +6166,7 @@
       <c r="O36" t="s">
         <v>200</v>
       </c>
-      <c r="P36" s="4" t="s">
+      <c r="P36" s="5" t="s">
         <v>201</v>
       </c>
       <c r="Q36" t="s">
@@ -6535,9 +6178,9 @@
       <c r="S36" t="s">
         <v>202</v>
       </c>
-      <c r="T36" s="7"/>
+      <c r="T36" s="6"/>
       <c r="U36" s="1">
-        <v>0.0736111111111111</v>
+        <v>7.3611111111111099E-2</v>
       </c>
       <c r="V36">
         <v>7</v>
@@ -6545,7 +6188,7 @@
       <c r="W36" t="s">
         <v>203</v>
       </c>
-      <c r="X36" s="3" t="s">
+      <c r="X36" s="4" t="s">
         <v>204</v>
       </c>
       <c r="Y36" t="s">
@@ -6557,7 +6200,7 @@
       <c r="AA36" t="s">
         <v>205</v>
       </c>
-      <c r="AB36" s="3" t="s">
+      <c r="AB36" s="4" t="s">
         <v>206</v>
       </c>
       <c r="AC36" t="s">
@@ -6603,7 +6246,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" ht="28.5" spans="1:43">
+    <row r="37" spans="1:43" ht="28" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -6614,7 +6257,7 @@
         <v>915</v>
       </c>
       <c r="F37" s="1">
-        <v>0.00138888888888889</v>
+        <v>1.38888888888889E-3</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -6623,7 +6266,7 @@
         <v>208</v>
       </c>
       <c r="I37" s="1">
-        <v>0.00902777777777778</v>
+        <v>9.0277777777777804E-3</v>
       </c>
       <c r="J37">
         <v>2</v>
@@ -6632,7 +6275,7 @@
         <v>209</v>
       </c>
       <c r="M37" s="1">
-        <v>0.0131944444444444</v>
+        <v>1.3194444444444399E-2</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -6640,11 +6283,11 @@
       <c r="O37" t="s">
         <v>210</v>
       </c>
-      <c r="P37" s="5" t="s">
+      <c r="P37" s="7" t="s">
         <v>211</v>
       </c>
       <c r="Q37" s="1">
-        <v>0.0666666666666667</v>
+        <v>6.6666666666666693E-2</v>
       </c>
       <c r="R37">
         <v>14</v>
@@ -6652,11 +6295,11 @@
       <c r="S37" t="s">
         <v>212</v>
       </c>
-      <c r="T37" s="4" t="s">
+      <c r="T37" s="5" t="s">
         <v>213</v>
       </c>
       <c r="U37" s="1">
-        <v>0.0770833333333333</v>
+        <v>7.7083333333333295E-2</v>
       </c>
       <c r="V37">
         <v>2</v>
@@ -6722,7 +6365,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" ht="58.5" spans="1:43">
+    <row r="38" spans="1:43" ht="56" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -6733,7 +6376,7 @@
         <v>920</v>
       </c>
       <c r="F38" s="1">
-        <v>0.00416666666666667</v>
+        <v>4.1666666666666701E-3</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -6742,7 +6385,7 @@
         <v>208</v>
       </c>
       <c r="I38" s="1">
-        <v>0.0138888888888889</v>
+        <v>1.38888888888889E-2</v>
       </c>
       <c r="J38">
         <v>2</v>
@@ -6751,7 +6394,7 @@
         <v>218</v>
       </c>
       <c r="M38" s="1">
-        <v>0.0173611111111111</v>
+        <v>1.7361111111111101E-2</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -6759,7 +6402,7 @@
       <c r="O38" t="s">
         <v>219</v>
       </c>
-      <c r="P38" s="6" t="s">
+      <c r="P38" s="8" t="s">
         <v>220</v>
       </c>
       <c r="Q38" t="s">
@@ -6771,7 +6414,7 @@
       <c r="S38" t="s">
         <v>221</v>
       </c>
-      <c r="T38" s="3" t="s">
+      <c r="T38" s="4" t="s">
         <v>222</v>
       </c>
       <c r="U38" t="s">
@@ -6787,7 +6430,7 @@
         <v>224</v>
       </c>
       <c r="Y38" s="1">
-        <v>0.0277777777777778</v>
+        <v>2.7777777777777801E-2</v>
       </c>
       <c r="Z38">
         <v>1</v>
@@ -6841,7 +6484,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" ht="75" spans="1:43">
+    <row r="39" spans="1:43" ht="70" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -6852,13 +6495,13 @@
         <v>938</v>
       </c>
       <c r="F39" s="1">
-        <v>0.00277777777777778</v>
+        <v>2.7777777777777801E-3</v>
       </c>
       <c r="G39">
         <v>2</v>
       </c>
       <c r="I39" s="1">
-        <v>0.00416666666666667</v>
+        <v>4.1666666666666701E-3</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -6866,7 +6509,7 @@
       <c r="K39" t="s">
         <v>228</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="L39" s="4" t="s">
         <v>229</v>
       </c>
       <c r="M39" t="s">
@@ -6882,7 +6525,7 @@
         <v>231</v>
       </c>
       <c r="Q39" s="1">
-        <v>0.0131944444444444</v>
+        <v>1.3194444444444399E-2</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -6890,7 +6533,7 @@
       <c r="S39" t="s">
         <v>232</v>
       </c>
-      <c r="T39" s="3" t="s">
+      <c r="T39" s="4" t="s">
         <v>233</v>
       </c>
       <c r="U39" t="s">
@@ -6902,7 +6545,7 @@
       <c r="W39" t="s">
         <v>234</v>
       </c>
-      <c r="X39" s="3" t="s">
+      <c r="X39" s="4" t="s">
         <v>235</v>
       </c>
       <c r="Y39" t="s">
@@ -6918,7 +6561,7 @@
         <v>237</v>
       </c>
       <c r="AC39" s="1">
-        <v>0.0444444444444444</v>
+        <v>4.4444444444444398E-2</v>
       </c>
       <c r="AD39">
         <v>2</v>
@@ -6960,7 +6603,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" ht="30" spans="1:43">
+    <row r="40" spans="1:43" ht="28" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -6971,7 +6614,7 @@
         <v>946</v>
       </c>
       <c r="F40" s="1">
-        <v>0.00625</v>
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -6980,7 +6623,7 @@
         <v>83</v>
       </c>
       <c r="I40" s="1">
-        <v>0.00902777777777778</v>
+        <v>9.0277777777777804E-3</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -6989,7 +6632,7 @@
         <v>239</v>
       </c>
       <c r="M40" s="1">
-        <v>0.0145833333333333</v>
+        <v>1.4583333333333301E-2</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -7001,7 +6644,7 @@
         <v>241</v>
       </c>
       <c r="Q40" s="1">
-        <v>0.0375</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="R40">
         <v>3</v>
@@ -7009,7 +6652,7 @@
       <c r="S40" t="s">
         <v>242</v>
       </c>
-      <c r="T40" s="3" t="s">
+      <c r="T40" s="4" t="s">
         <v>243</v>
       </c>
       <c r="U40" t="s">
@@ -7073,7 +6716,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:43">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -7084,13 +6727,13 @@
         <v>954</v>
       </c>
       <c r="F41" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="I41" s="1">
-        <v>0.00833333333333333</v>
+        <v>8.3333333333333297E-3</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -7099,7 +6742,7 @@
         <v>245</v>
       </c>
       <c r="M41" s="1">
-        <v>0.05625</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="N41">
         <v>5</v>
@@ -7111,7 +6754,7 @@
         <v>247</v>
       </c>
       <c r="Q41" s="1">
-        <v>0.0215277777777778</v>
+        <v>2.1527777777777798E-2</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -7123,7 +6766,7 @@
         <v>249</v>
       </c>
       <c r="U41" s="1">
-        <v>0.0958333333333333</v>
+        <v>9.5833333333333298E-2</v>
       </c>
       <c r="V41">
         <v>7</v>
@@ -7144,7 +6787,7 @@
         <v>252</v>
       </c>
       <c r="AC41" s="1">
-        <v>0.0395833333333333</v>
+        <v>3.9583333333333297E-2</v>
       </c>
       <c r="AD41">
         <v>3</v>
@@ -7189,7 +6832,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:43">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>41</v>
       </c>
@@ -7197,19 +6840,19 @@
         <v>961</v>
       </c>
       <c r="F42" s="1">
-        <v>0.00138888888888889</v>
+        <v>1.38888888888889E-3</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="I42" s="1">
-        <v>0.00416666666666667</v>
+        <v>4.1666666666666701E-3</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="M42" s="1">
-        <v>0.0111111111111111</v>
+        <v>1.1111111111111099E-2</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -7221,7 +6864,7 @@
         <v>256</v>
       </c>
       <c r="Q42" s="1">
-        <v>0.0604166666666667</v>
+        <v>6.0416666666666702E-2</v>
       </c>
       <c r="R42">
         <v>4</v>
@@ -7230,7 +6873,7 @@
         <v>112</v>
       </c>
       <c r="U42" s="1">
-        <v>0.0534722222222222</v>
+        <v>5.3472222222222199E-2</v>
       </c>
       <c r="V42">
         <v>2</v>
@@ -7293,7 +6936,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="2:43">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>42</v>
       </c>
@@ -7328,7 +6971,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="2:43">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B44">
         <v>43</v>
       </c>
@@ -7360,7 +7003,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="2:43">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>44</v>
       </c>
@@ -7392,7 +7035,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="2:43">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B46">
         <v>45</v>
       </c>
@@ -7424,7 +7067,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="2:43">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>46</v>
       </c>
@@ -7456,7 +7099,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="2:43">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>47</v>
       </c>
@@ -7488,7 +7131,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="2:43">
+    <row r="49" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>48</v>
       </c>
@@ -7520,7 +7163,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="2:43">
+    <row r="50" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>49</v>
       </c>
@@ -7552,7 +7195,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="2:43">
+    <row r="51" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>50</v>
       </c>
@@ -7584,7 +7227,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="2:43">
+    <row r="52" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B52">
         <v>51</v>
       </c>
@@ -7616,7 +7259,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="2:43">
+    <row r="53" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>52</v>
       </c>
@@ -7648,7 +7291,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="2:43">
+    <row r="54" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>53</v>
       </c>
@@ -7680,7 +7323,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="2:43">
+    <row r="55" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>54</v>
       </c>
@@ -7712,7 +7355,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="2:43">
+    <row r="56" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>55</v>
       </c>
@@ -7744,7 +7387,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="2:43">
+    <row r="57" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>56</v>
       </c>
@@ -7776,7 +7419,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="2:43">
+    <row r="58" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B58">
         <v>57</v>
       </c>
@@ -7808,7 +7451,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="2:43">
+    <row r="59" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>58</v>
       </c>
@@ -7840,7 +7483,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="2:43">
+    <row r="60" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>59</v>
       </c>
@@ -7872,7 +7515,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="2:43">
+    <row r="61" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>60</v>
       </c>
@@ -7904,7 +7547,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="2:43">
+    <row r="62" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>61</v>
       </c>
@@ -7936,7 +7579,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="2:43">
+    <row r="63" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>62</v>
       </c>
@@ -7968,7 +7611,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="2:43">
+    <row r="64" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>63</v>
       </c>
@@ -8000,7 +7643,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="2:43">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>64</v>
       </c>
@@ -8032,7 +7675,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="2:43">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>65</v>
       </c>
@@ -8064,7 +7707,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="2:43">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>66</v>
       </c>
@@ -8096,7 +7739,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="2:43">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>67</v>
       </c>
@@ -8128,7 +7771,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="2:43">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B69">
         <v>68</v>
       </c>
@@ -8160,7 +7803,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="2:43">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>69</v>
       </c>
@@ -8192,7 +7835,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="2:43">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>70</v>
       </c>
@@ -8224,7 +7867,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="2:43">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>71</v>
       </c>
@@ -8232,13 +7875,13 @@
         <v>1207</v>
       </c>
       <c r="F72" s="1">
-        <v>0.00208333333333333</v>
+        <v>2.0833333333333298E-3</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="I72" s="1">
-        <v>0.00555555555555556</v>
+        <v>5.5555555555555601E-3</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -8247,7 +7890,7 @@
         <v>259</v>
       </c>
       <c r="M72" s="1">
-        <v>0.0201388888888889</v>
+        <v>2.0138888888888901E-2</v>
       </c>
       <c r="N72">
         <v>1</v>
@@ -8256,7 +7899,7 @@
         <v>260</v>
       </c>
       <c r="Q72" s="1">
-        <v>0.0423611111111111</v>
+        <v>4.2361111111111099E-2</v>
       </c>
       <c r="R72">
         <v>3</v>
@@ -8331,7 +7974,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" ht="60" spans="2:43">
+    <row r="73" spans="2:43" ht="56" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>72</v>
       </c>
@@ -8339,13 +7982,13 @@
         <v>1217</v>
       </c>
       <c r="F73" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="I73" s="1">
-        <v>0.0104166666666667</v>
+        <v>1.0416666666666701E-2</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -8389,7 +8032,7 @@
       <c r="W73" t="s">
         <v>273</v>
       </c>
-      <c r="X73" s="3" t="s">
+      <c r="X73" s="4" t="s">
         <v>274</v>
       </c>
       <c r="Y73" t="s">
@@ -8450,7 +8093,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74" ht="90" spans="2:43">
+    <row r="74" spans="2:43" ht="84" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>73</v>
       </c>
@@ -8458,7 +8101,7 @@
         <v>1221</v>
       </c>
       <c r="F74" s="1">
-        <v>0.00208333333333333</v>
+        <v>2.0833333333333298E-3</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -8467,7 +8110,7 @@
         <v>277</v>
       </c>
       <c r="I74" s="1">
-        <v>0.0131944444444444</v>
+        <v>1.3194444444444399E-2</v>
       </c>
       <c r="J74">
         <v>2</v>
@@ -8476,16 +8119,16 @@
         <v>30</v>
       </c>
       <c r="M74" s="1">
-        <v>0.00972222222222222</v>
+        <v>9.7222222222222206E-3</v>
       </c>
       <c r="O74" t="s">
         <v>278</v>
       </c>
-      <c r="P74" s="3" t="s">
+      <c r="P74" s="4" t="s">
         <v>279</v>
       </c>
       <c r="Q74" s="1">
-        <v>0.0215277777777778</v>
+        <v>2.1527777777777798E-2</v>
       </c>
       <c r="R74">
         <v>1</v>
@@ -8493,11 +8136,11 @@
       <c r="S74" t="s">
         <v>280</v>
       </c>
-      <c r="T74" s="3" t="s">
+      <c r="T74" s="4" t="s">
         <v>281</v>
       </c>
       <c r="U74" s="1">
-        <v>0.0527777777777778</v>
+        <v>5.2777777777777798E-2</v>
       </c>
       <c r="V74">
         <v>4</v>
@@ -8554,7 +8197,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" ht="90" spans="2:43">
+    <row r="75" spans="2:43" ht="70" x14ac:dyDescent="0.25">
       <c r="B75">
         <v>74</v>
       </c>
@@ -8562,7 +8205,7 @@
         <v>1238</v>
       </c>
       <c r="F75" s="1">
-        <v>0.00138888888888889</v>
+        <v>1.38888888888889E-3</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -8571,7 +8214,7 @@
         <v>30</v>
       </c>
       <c r="I75" s="1">
-        <v>0.00625</v>
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -8583,7 +8226,7 @@
         <v>282</v>
       </c>
       <c r="M75" s="1">
-        <v>0.0444444444444444</v>
+        <v>4.4444444444444398E-2</v>
       </c>
       <c r="N75">
         <v>1</v>
@@ -8595,7 +8238,7 @@
         <v>284</v>
       </c>
       <c r="Q75" s="1">
-        <v>0.0708333333333333</v>
+        <v>7.0833333333333304E-2</v>
       </c>
       <c r="R75">
         <v>2</v>
@@ -8603,7 +8246,7 @@
       <c r="S75" t="s">
         <v>285</v>
       </c>
-      <c r="T75" s="3" t="s">
+      <c r="T75" s="4" t="s">
         <v>286</v>
       </c>
       <c r="U75" t="s">
@@ -8615,7 +8258,7 @@
       <c r="W75" t="s">
         <v>287</v>
       </c>
-      <c r="X75" s="3" t="s">
+      <c r="X75" s="4" t="s">
         <v>288</v>
       </c>
       <c r="Y75" t="s">
@@ -8670,7 +8313,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" ht="255" spans="2:43">
+    <row r="76" spans="2:43" ht="238" x14ac:dyDescent="0.25">
       <c r="B76">
         <v>75</v>
       </c>
@@ -8678,13 +8321,13 @@
         <v>1251</v>
       </c>
       <c r="F76" s="1">
-        <v>0.00486111111111111</v>
+        <v>4.8611111111111103E-3</v>
       </c>
       <c r="G76">
         <v>3</v>
       </c>
       <c r="I76" s="1">
-        <v>0.01875</v>
+        <v>1.8749999999999999E-2</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -8693,7 +8336,7 @@
         <v>169</v>
       </c>
       <c r="M76" s="1">
-        <v>0.0256944444444444</v>
+        <v>2.5694444444444402E-2</v>
       </c>
       <c r="N76">
         <v>1</v>
@@ -8701,11 +8344,11 @@
       <c r="O76" t="s">
         <v>30</v>
       </c>
-      <c r="P76" s="3" t="s">
+      <c r="P76" s="4" t="s">
         <v>290</v>
       </c>
       <c r="Q76" s="1">
-        <v>0.0319444444444444</v>
+        <v>3.19444444444444E-2</v>
       </c>
       <c r="R76">
         <v>1</v>
@@ -8722,7 +8365,7 @@
       <c r="W76" t="s">
         <v>292</v>
       </c>
-      <c r="X76" s="3" t="s">
+      <c r="X76" s="4" t="s">
         <v>293</v>
       </c>
       <c r="Y76" t="s">
@@ -8731,13 +8374,13 @@
       <c r="Z76">
         <v>-1</v>
       </c>
-      <c r="AA76" s="8" t="s">
+      <c r="AA76" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AB76" t="s">
         <v>25</v>
       </c>
-      <c r="AC76" s="8" t="s">
+      <c r="AC76" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AD76" t="s">
@@ -8783,7 +8426,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" ht="73.5" spans="2:43">
+    <row r="77" spans="2:43" ht="56" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>76</v>
       </c>
@@ -8791,7 +8434,7 @@
         <v>1257</v>
       </c>
       <c r="F77" s="1">
-        <v>0.00555555555555556</v>
+        <v>5.5555555555555601E-3</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -8800,7 +8443,7 @@
         <v>294</v>
       </c>
       <c r="I77" s="1">
-        <v>0.0111111111111111</v>
+        <v>1.1111111111111099E-2</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -8809,7 +8452,7 @@
         <v>169</v>
       </c>
       <c r="M77" s="1">
-        <v>0.0180555555555556</v>
+        <v>1.8055555555555599E-2</v>
       </c>
       <c r="N77">
         <v>1</v>
@@ -8817,11 +8460,11 @@
       <c r="O77" t="s">
         <v>295</v>
       </c>
-      <c r="P77" s="3" t="s">
+      <c r="P77" s="4" t="s">
         <v>296</v>
       </c>
       <c r="Q77" s="1">
-        <v>0.0305555555555556</v>
+        <v>3.05555555555556E-2</v>
       </c>
       <c r="R77">
         <v>2</v>
@@ -8829,7 +8472,7 @@
       <c r="S77" t="s">
         <v>297</v>
       </c>
-      <c r="T77" s="3" t="s">
+      <c r="T77" s="4" t="s">
         <v>298</v>
       </c>
       <c r="U77" t="s">
@@ -8841,7 +8484,7 @@
       <c r="W77" t="s">
         <v>299</v>
       </c>
-      <c r="X77" s="3" t="s">
+      <c r="X77" s="4" t="s">
         <v>300</v>
       </c>
       <c r="Y77" t="s">
@@ -8902,7 +8545,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" ht="72" spans="2:43">
+    <row r="78" spans="2:43" ht="70" x14ac:dyDescent="0.25">
       <c r="B78">
         <v>77</v>
       </c>
@@ -8910,13 +8553,13 @@
         <v>1260</v>
       </c>
       <c r="F78" s="1">
-        <v>0.00416666666666667</v>
+        <v>4.1666666666666701E-3</v>
       </c>
       <c r="G78">
         <v>1</v>
       </c>
       <c r="I78" s="1">
-        <v>0.00902777777777778</v>
+        <v>9.0277777777777804E-3</v>
       </c>
       <c r="J78">
         <v>2</v>
@@ -8928,7 +8571,7 @@
         <v>304</v>
       </c>
       <c r="M78" s="1">
-        <v>0.0506944444444444</v>
+        <v>5.0694444444444403E-2</v>
       </c>
       <c r="N78">
         <v>2</v>
@@ -8948,7 +8591,7 @@
       <c r="S78" t="s">
         <v>306</v>
       </c>
-      <c r="T78" s="3" t="s">
+      <c r="T78" s="4" t="s">
         <v>307</v>
       </c>
       <c r="U78" t="s">
@@ -9021,7 +8664,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" ht="30" spans="2:43">
+    <row r="79" spans="2:43" ht="28" x14ac:dyDescent="0.25">
       <c r="B79">
         <v>78</v>
       </c>
@@ -9029,13 +8672,13 @@
         <v>1278</v>
       </c>
       <c r="F79" s="1">
-        <v>0.00277777777777778</v>
+        <v>2.7777777777777801E-3</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="I79" s="1">
-        <v>0.0131944444444444</v>
+        <v>1.3194444444444399E-2</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -9044,7 +8687,7 @@
         <v>310</v>
       </c>
       <c r="M79" s="1">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="N79">
         <v>2</v>
@@ -9052,11 +8695,11 @@
       <c r="O79" t="s">
         <v>311</v>
       </c>
-      <c r="P79" s="3" t="s">
+      <c r="P79" s="4" t="s">
         <v>312</v>
       </c>
       <c r="Q79" s="1">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="R79">
         <v>1</v>
@@ -9137,7 +8780,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" ht="30" spans="2:43">
+    <row r="80" spans="2:43" ht="28" x14ac:dyDescent="0.25">
       <c r="B80">
         <v>79</v>
       </c>
@@ -9145,7 +8788,7 @@
         <v>1279</v>
       </c>
       <c r="F80" s="1">
-        <v>0.00208333333333333</v>
+        <v>2.0833333333333298E-3</v>
       </c>
       <c r="G80">
         <v>2</v>
@@ -9154,7 +8797,7 @@
         <v>30</v>
       </c>
       <c r="I80" s="1">
-        <v>0.00902777777777778</v>
+        <v>9.0277777777777804E-3</v>
       </c>
       <c r="J80">
         <v>2</v>
@@ -9163,7 +8806,7 @@
         <v>317</v>
       </c>
       <c r="M80" s="1">
-        <v>0.0173611111111111</v>
+        <v>1.7361111111111101E-2</v>
       </c>
       <c r="N80">
         <v>1</v>
@@ -9175,7 +8818,7 @@
         <v>319</v>
       </c>
       <c r="Q80" s="1">
-        <v>0.0326388888888889</v>
+        <v>3.2638888888888898E-2</v>
       </c>
       <c r="R80">
         <v>1</v>
@@ -9192,7 +8835,7 @@
       <c r="W80" t="s">
         <v>320</v>
       </c>
-      <c r="X80" s="3" t="s">
+      <c r="X80" s="4" t="s">
         <v>321</v>
       </c>
       <c r="Y80" t="s">
@@ -9253,7 +8896,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="2:43">
+    <row r="81" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B81">
         <v>80</v>
       </c>
@@ -9264,7 +8907,7 @@
         <v>322</v>
       </c>
       <c r="F81" s="1">
-        <v>0.0208333333333333</v>
+        <v>2.0833333333333301E-2</v>
       </c>
       <c r="G81">
         <v>7</v>
@@ -9273,7 +8916,7 @@
         <v>323</v>
       </c>
       <c r="I81" s="1">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J81">
         <v>1</v>
@@ -9285,7 +8928,7 @@
         <v>324</v>
       </c>
       <c r="M81" s="1">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="N81">
         <v>1</v>
@@ -9297,7 +8940,7 @@
         <v>326</v>
       </c>
       <c r="Q81" s="1">
-        <v>0.0520833333333333</v>
+        <v>5.2083333333333301E-2</v>
       </c>
       <c r="R81">
         <v>1</v>
@@ -9309,7 +8952,7 @@
         <v>328</v>
       </c>
       <c r="U81" s="1">
-        <v>0.0840277777777778</v>
+        <v>8.4027777777777798E-2</v>
       </c>
       <c r="V81">
         <v>4</v>
@@ -9378,7 +9021,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" ht="45" spans="2:43">
+    <row r="82" spans="2:43" ht="42" x14ac:dyDescent="0.25">
       <c r="B82">
         <v>81</v>
       </c>
@@ -9386,16 +9029,16 @@
         <v>1295</v>
       </c>
       <c r="F82" s="1">
-        <v>0.000694444444444444</v>
+        <v>6.9444444444444404E-4</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
-      <c r="H82" s="3" t="s">
+      <c r="H82" s="4" t="s">
         <v>330</v>
       </c>
       <c r="I82" s="1">
-        <v>0.00902777777777778</v>
+        <v>9.0277777777777804E-3</v>
       </c>
       <c r="J82">
         <v>2</v>
@@ -9407,7 +9050,7 @@
         <v>332</v>
       </c>
       <c r="M82" s="1">
-        <v>0.0173611111111111</v>
+        <v>1.7361111111111101E-2</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -9415,11 +9058,11 @@
       <c r="O82" t="s">
         <v>333</v>
       </c>
-      <c r="P82" s="3" t="s">
+      <c r="P82" s="4" t="s">
         <v>334</v>
       </c>
       <c r="Q82" s="1">
-        <v>0.0506944444444444</v>
+        <v>5.0694444444444403E-2</v>
       </c>
       <c r="R82">
         <v>1</v>
@@ -9494,7 +9137,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" ht="45" spans="2:43">
+    <row r="83" spans="2:43" ht="42" x14ac:dyDescent="0.25">
       <c r="B83">
         <v>82</v>
       </c>
@@ -9502,13 +9145,13 @@
         <v>1303</v>
       </c>
       <c r="F83" s="1">
-        <v>0.00277777777777778</v>
+        <v>2.7777777777777801E-3</v>
       </c>
       <c r="G83">
         <v>1</v>
       </c>
       <c r="I83" s="1">
-        <v>0.00625</v>
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="J83">
         <v>1</v>
@@ -9516,11 +9159,11 @@
       <c r="K83" t="s">
         <v>335</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="L83" s="4" t="s">
         <v>336</v>
       </c>
       <c r="M83" s="1">
-        <v>0.01875</v>
+        <v>1.8749999999999999E-2</v>
       </c>
       <c r="N83">
         <v>3</v>
@@ -9528,11 +9171,11 @@
       <c r="O83" t="s">
         <v>337</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="P83" s="4" t="s">
         <v>338</v>
       </c>
       <c r="Q83" s="1">
-        <v>0.03125</v>
+        <v>3.125E-2</v>
       </c>
       <c r="R83">
         <v>1</v>
@@ -9540,7 +9183,7 @@
       <c r="S83" t="s">
         <v>181</v>
       </c>
-      <c r="T83" s="3" t="s">
+      <c r="T83" s="4" t="s">
         <v>339</v>
       </c>
       <c r="U83" t="s">
@@ -9552,7 +9195,7 @@
       <c r="W83" t="s">
         <v>340</v>
       </c>
-      <c r="X83" s="3" t="s">
+      <c r="X83" s="4" t="s">
         <v>341</v>
       </c>
       <c r="Y83" t="s">
@@ -9610,7 +9253,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" ht="71.25" spans="2:43">
+    <row r="84" spans="2:43" ht="69" x14ac:dyDescent="0.25">
       <c r="B84">
         <v>83</v>
       </c>
@@ -9618,13 +9261,13 @@
         <v>1312</v>
       </c>
       <c r="F84" s="1">
-        <v>0.00138888888888889</v>
+        <v>1.38888888888889E-3</v>
       </c>
       <c r="G84">
         <v>1</v>
       </c>
       <c r="I84" s="1">
-        <v>0.00277777777777778</v>
+        <v>2.7777777777777801E-3</v>
       </c>
       <c r="J84">
         <v>1</v>
@@ -9636,7 +9279,7 @@
         <v>343</v>
       </c>
       <c r="M84" s="1">
-        <v>0.0159722222222222</v>
+        <v>1.59722222222222E-2</v>
       </c>
       <c r="N84">
         <v>2</v>
@@ -9648,7 +9291,7 @@
         <v>344</v>
       </c>
       <c r="Q84" s="1">
-        <v>0.0326388888888889</v>
+        <v>3.2638888888888898E-2</v>
       </c>
       <c r="R84">
         <v>1</v>
@@ -9656,11 +9299,11 @@
       <c r="S84" t="s">
         <v>345</v>
       </c>
-      <c r="T84" s="3" t="s">
+      <c r="T84" s="4" t="s">
         <v>346</v>
       </c>
       <c r="U84" s="1">
-        <v>0.0701388888888889</v>
+        <v>7.0138888888888903E-2</v>
       </c>
       <c r="V84">
         <v>5</v>
@@ -9680,7 +9323,7 @@
       <c r="AA84" t="s">
         <v>347</v>
       </c>
-      <c r="AB84" s="5" t="s">
+      <c r="AB84" s="7" t="s">
         <v>348</v>
       </c>
       <c r="AC84" t="s">
@@ -9729,7 +9372,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" ht="60" spans="2:43">
+    <row r="85" spans="2:43" ht="70" x14ac:dyDescent="0.25">
       <c r="B85">
         <v>84</v>
       </c>
@@ -9737,7 +9380,7 @@
         <v>1327</v>
       </c>
       <c r="F85" s="1">
-        <v>0.00138888888888889</v>
+        <v>1.38888888888889E-3</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -9746,7 +9389,7 @@
         <v>83</v>
       </c>
       <c r="I85" s="1">
-        <v>0.00486111111111111</v>
+        <v>4.8611111111111103E-3</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -9758,7 +9401,7 @@
         <v>350</v>
       </c>
       <c r="M85" s="1">
-        <v>0.0277777777777778</v>
+        <v>2.7777777777777801E-2</v>
       </c>
       <c r="N85">
         <v>4</v>
@@ -9770,7 +9413,7 @@
         <v>352</v>
       </c>
       <c r="Q85" s="1">
-        <v>0.0777777777777778</v>
+        <v>7.7777777777777807E-2</v>
       </c>
       <c r="R85">
         <v>3</v>
@@ -9782,7 +9425,7 @@
         <v>354</v>
       </c>
       <c r="U85" s="1">
-        <v>0.04375</v>
+        <v>4.3749999999999997E-2</v>
       </c>
       <c r="V85">
         <v>2</v>
@@ -9790,7 +9433,7 @@
       <c r="W85" t="s">
         <v>355</v>
       </c>
-      <c r="X85" s="3" t="s">
+      <c r="X85" s="4" t="s">
         <v>356</v>
       </c>
       <c r="Y85" t="s">
@@ -9851,7 +9494,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" ht="30" spans="2:43">
+    <row r="86" spans="2:43" ht="28" x14ac:dyDescent="0.25">
       <c r="B86">
         <v>85</v>
       </c>
@@ -9859,13 +9502,13 @@
         <v>1334</v>
       </c>
       <c r="F86" s="1">
-        <v>0.00277777777777778</v>
+        <v>2.7777777777777801E-3</v>
       </c>
       <c r="G86">
         <v>1</v>
       </c>
       <c r="I86" s="1">
-        <v>0.00555555555555556</v>
+        <v>5.5555555555555601E-3</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -9877,7 +9520,7 @@
         <v>358</v>
       </c>
       <c r="M86" s="1">
-        <v>0.0236111111111111</v>
+        <v>2.36111111111111E-2</v>
       </c>
       <c r="N86">
         <v>2</v>
@@ -9889,7 +9532,7 @@
         <v>359</v>
       </c>
       <c r="Q86" s="1">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="R86">
         <v>1</v>
@@ -9897,7 +9540,7 @@
       <c r="S86" t="s">
         <v>360</v>
       </c>
-      <c r="T86" s="3" t="s">
+      <c r="T86" s="4" t="s">
         <v>361</v>
       </c>
       <c r="U86" t="s">
@@ -9909,7 +9552,7 @@
       <c r="W86" t="s">
         <v>362</v>
       </c>
-      <c r="X86" s="3" t="s">
+      <c r="X86" s="4" t="s">
         <v>363</v>
       </c>
       <c r="Y86" t="s">
@@ -9964,7 +9607,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" ht="75" spans="2:43">
+    <row r="87" spans="2:43" ht="70" x14ac:dyDescent="0.25">
       <c r="B87">
         <v>86</v>
       </c>
@@ -9972,7 +9615,7 @@
         <v>1342</v>
       </c>
       <c r="F87" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -9981,7 +9624,7 @@
         <v>364</v>
       </c>
       <c r="I87" s="1">
-        <v>0.0111111111111111</v>
+        <v>1.1111111111111099E-2</v>
       </c>
       <c r="J87">
         <v>1</v>
@@ -9993,7 +9636,7 @@
         <v>366</v>
       </c>
       <c r="M87" s="1">
-        <v>0.0236111111111111</v>
+        <v>2.36111111111111E-2</v>
       </c>
       <c r="N87">
         <v>2</v>
@@ -10001,7 +9644,7 @@
       <c r="O87" t="s">
         <v>251</v>
       </c>
-      <c r="P87" s="3" t="s">
+      <c r="P87" s="4" t="s">
         <v>367</v>
       </c>
       <c r="Q87" s="1">
@@ -10013,7 +9656,7 @@
       <c r="S87" t="s">
         <v>368</v>
       </c>
-      <c r="T87" s="3" t="s">
+      <c r="T87" s="4" t="s">
         <v>369</v>
       </c>
       <c r="U87" t="s">
@@ -10086,7 +9729,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" ht="45" spans="2:43">
+    <row r="88" spans="2:43" ht="42" x14ac:dyDescent="0.25">
       <c r="B88">
         <v>87</v>
       </c>
@@ -10094,7 +9737,7 @@
         <v>1354</v>
       </c>
       <c r="F88" s="1">
-        <v>0.00486111111111111</v>
+        <v>4.8611111111111103E-3</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -10103,7 +9746,7 @@
         <v>370</v>
       </c>
       <c r="I88" s="1">
-        <v>0.0159722222222222</v>
+        <v>1.59722222222222E-2</v>
       </c>
       <c r="J88">
         <v>1</v>
@@ -10132,7 +9775,7 @@
       <c r="S88" t="s">
         <v>374</v>
       </c>
-      <c r="T88" s="3" t="s">
+      <c r="T88" s="4" t="s">
         <v>375</v>
       </c>
       <c r="U88" t="s">
@@ -10148,7 +9791,7 @@
         <v>377</v>
       </c>
       <c r="Y88" s="1">
-        <v>0.0819444444444444</v>
+        <v>8.1944444444444403E-2</v>
       </c>
       <c r="Z88">
         <v>1</v>
@@ -10205,7 +9848,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89" ht="30" spans="2:43">
+    <row r="89" spans="2:43" ht="28" x14ac:dyDescent="0.25">
       <c r="B89">
         <v>88</v>
       </c>
@@ -10213,7 +9856,7 @@
         <v>1359</v>
       </c>
       <c r="F89" s="1">
-        <v>0.00694444444444444</v>
+        <v>6.9444444444444397E-3</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -10222,7 +9865,7 @@
         <v>83</v>
       </c>
       <c r="I89" s="1">
-        <v>0.0111111111111111</v>
+        <v>1.1111111111111099E-2</v>
       </c>
       <c r="J89">
         <v>1</v>
@@ -10246,7 +9889,7 @@
         <v>385</v>
       </c>
       <c r="Q89" s="1">
-        <v>0.0729166666666667</v>
+        <v>7.2916666666666699E-2</v>
       </c>
       <c r="R89">
         <v>2</v>
@@ -10254,7 +9897,7 @@
       <c r="S89" t="s">
         <v>386</v>
       </c>
-      <c r="T89" s="3" t="s">
+      <c r="T89" s="4" t="s">
         <v>387</v>
       </c>
       <c r="U89" t="s">
@@ -10327,7 +9970,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" ht="88.5" spans="2:43">
+    <row r="90" spans="2:43" ht="56" x14ac:dyDescent="0.25">
       <c r="B90">
         <v>89</v>
       </c>
@@ -10338,7 +9981,7 @@
         <v>389</v>
       </c>
       <c r="F90" s="1">
-        <v>0.0111111111111111</v>
+        <v>1.1111111111111099E-2</v>
       </c>
       <c r="G90">
         <v>2</v>
@@ -10347,7 +9990,7 @@
         <v>169</v>
       </c>
       <c r="I90" s="1">
-        <v>0.0243055555555556</v>
+        <v>2.4305555555555601E-2</v>
       </c>
       <c r="J90">
         <v>1</v>
@@ -10356,7 +9999,7 @@
         <v>169</v>
       </c>
       <c r="M90" s="1">
-        <v>0.0333333333333333</v>
+        <v>3.3333333333333298E-2</v>
       </c>
       <c r="N90">
         <v>1</v>
@@ -10368,7 +10011,7 @@
         <v>390</v>
       </c>
       <c r="Q90" s="1">
-        <v>0.0618055555555556</v>
+        <v>6.18055555555556E-2</v>
       </c>
       <c r="R90">
         <v>3</v>
@@ -10380,7 +10023,7 @@
         <v>392</v>
       </c>
       <c r="U90" s="1">
-        <v>0.0708333333333333</v>
+        <v>7.0833333333333304E-2</v>
       </c>
       <c r="V90">
         <v>2</v>
@@ -10388,7 +10031,7 @@
       <c r="W90" t="s">
         <v>393</v>
       </c>
-      <c r="X90" s="9" t="s">
+      <c r="X90" s="4" t="s">
         <v>394</v>
       </c>
       <c r="Y90" t="s">
@@ -10400,7 +10043,7 @@
       <c r="AA90" t="s">
         <v>395</v>
       </c>
-      <c r="AB90" s="9" t="s">
+      <c r="AB90" s="4" t="s">
         <v>396</v>
       </c>
       <c r="AC90" t="s">
@@ -10449,7 +10092,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" ht="60" spans="2:43">
+    <row r="91" spans="2:43" ht="42" x14ac:dyDescent="0.25">
       <c r="B91">
         <v>90</v>
       </c>
@@ -10457,7 +10100,7 @@
         <v>1373</v>
       </c>
       <c r="F91" s="1">
-        <v>0.00347222222222222</v>
+        <v>3.4722222222222199E-3</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -10466,7 +10109,7 @@
         <v>169</v>
       </c>
       <c r="I91" s="1">
-        <v>0.00694444444444444</v>
+        <v>6.9444444444444397E-3</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -10475,7 +10118,7 @@
         <v>169</v>
       </c>
       <c r="M91" s="1">
-        <v>0.0159722222222222</v>
+        <v>1.59722222222222E-2</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -10484,7 +10127,7 @@
         <v>397</v>
       </c>
       <c r="Q91" s="1">
-        <v>0.0291666666666667</v>
+        <v>2.9166666666666698E-2</v>
       </c>
       <c r="R91">
         <v>1</v>
@@ -10516,7 +10159,7 @@
       <c r="AA91" t="s">
         <v>402</v>
       </c>
-      <c r="AB91" s="9" t="s">
+      <c r="AB91" s="4" t="s">
         <v>403</v>
       </c>
       <c r="AC91" t="s">
@@ -10565,7 +10208,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" ht="60" spans="2:43">
+    <row r="92" spans="2:43" ht="56" x14ac:dyDescent="0.25">
       <c r="B92">
         <v>91</v>
       </c>
@@ -10573,7 +10216,7 @@
         <v>1380</v>
       </c>
       <c r="F92" s="1">
-        <v>0.00416666666666667</v>
+        <v>4.1666666666666701E-3</v>
       </c>
       <c r="G92">
         <v>2</v>
@@ -10582,7 +10225,7 @@
         <v>404</v>
       </c>
       <c r="I92" s="1">
-        <v>0.00833333333333333</v>
+        <v>8.3333333333333297E-3</v>
       </c>
       <c r="J92">
         <v>1</v>
@@ -10591,7 +10234,7 @@
         <v>169</v>
       </c>
       <c r="M92" s="1">
-        <v>0.0138888888888889</v>
+        <v>1.38888888888889E-2</v>
       </c>
       <c r="N92">
         <v>1</v>
@@ -10603,7 +10246,7 @@
         <v>405</v>
       </c>
       <c r="Q92" s="1">
-        <v>0.0402777777777778</v>
+        <v>4.0277777777777801E-2</v>
       </c>
       <c r="R92">
         <v>2</v>
@@ -10611,11 +10254,11 @@
       <c r="S92" t="s">
         <v>406</v>
       </c>
-      <c r="T92" s="9" t="s">
+      <c r="T92" s="4" t="s">
         <v>407</v>
       </c>
       <c r="U92" s="1">
-        <v>0.0631944444444444</v>
+        <v>6.31944444444444E-2</v>
       </c>
       <c r="V92">
         <v>3</v>
@@ -10623,7 +10266,7 @@
       <c r="W92" t="s">
         <v>408</v>
       </c>
-      <c r="X92" s="9" t="s">
+      <c r="X92" s="4" t="s">
         <v>409</v>
       </c>
       <c r="Y92" t="s">
@@ -10678,33 +10321,899 @@
         <v>91</v>
       </c>
     </row>
+    <row r="93" spans="2:43" ht="182" x14ac:dyDescent="0.25">
+      <c r="B93">
+        <v>92</v>
+      </c>
+      <c r="D93">
+        <v>1389</v>
+      </c>
+      <c r="F93" s="1">
+        <v>1.38888888888889E-3</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93" t="s">
+        <v>410</v>
+      </c>
+      <c r="I93" s="1">
+        <v>1.1111111111111099E-2</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93" t="s">
+        <v>169</v>
+      </c>
+      <c r="L93" t="s">
+        <v>411</v>
+      </c>
+      <c r="M93" s="1">
+        <v>2.7777777777777801E-2</v>
+      </c>
+      <c r="N93">
+        <v>4</v>
+      </c>
+      <c r="O93" t="s">
+        <v>412</v>
+      </c>
+      <c r="P93" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q93" s="1">
+        <v>6.7361111111111094E-2</v>
+      </c>
+      <c r="R93">
+        <v>4</v>
+      </c>
+      <c r="S93" t="s">
+        <v>414</v>
+      </c>
+      <c r="T93" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="U93" t="s">
+        <v>22</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93" t="s">
+        <v>416</v>
+      </c>
+      <c r="X93" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y93" s="1">
+        <v>8.6805555555555594E-2</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>418</v>
+      </c>
+      <c r="AC93" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD93">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="s">
+        <v>419</v>
+      </c>
+      <c r="AF93" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG93">
+        <v>800</v>
+      </c>
+      <c r="AH93">
+        <v>1600</v>
+      </c>
+      <c r="AI93">
+        <v>1500</v>
+      </c>
+      <c r="AJ93">
+        <v>2100</v>
+      </c>
+      <c r="AK93">
+        <v>2200</v>
+      </c>
+      <c r="AL93">
+        <v>2600</v>
+      </c>
+      <c r="AM93">
+        <v>2800</v>
+      </c>
+      <c r="AN93" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO93" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP93">
+        <v>1389</v>
+      </c>
+      <c r="AQ93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="2:43" ht="28" x14ac:dyDescent="0.25">
+      <c r="B94">
+        <v>93</v>
+      </c>
+      <c r="D94">
+        <v>1398</v>
+      </c>
+      <c r="F94" s="1">
+        <v>1.38888888888889E-3</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="I94" s="1">
+        <v>3.4722222222222199E-3</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="M94" s="1">
+        <v>6.9444444444444397E-3</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94" t="s">
+        <v>244</v>
+      </c>
+      <c r="P94" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q94" s="1">
+        <v>4.2361111111111099E-2</v>
+      </c>
+      <c r="R94">
+        <v>3</v>
+      </c>
+      <c r="S94" t="s">
+        <v>421</v>
+      </c>
+      <c r="T94" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="U94" s="1">
+        <v>6.5972222222222196E-2</v>
+      </c>
+      <c r="V94">
+        <v>2</v>
+      </c>
+      <c r="W94" t="s">
+        <v>423</v>
+      </c>
+      <c r="X94" t="s">
+        <v>424</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD94">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF94" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG94">
+        <v>800</v>
+      </c>
+      <c r="AH94">
+        <v>800</v>
+      </c>
+      <c r="AI94">
+        <v>1600</v>
+      </c>
+      <c r="AJ94">
+        <v>1800</v>
+      </c>
+      <c r="AK94">
+        <v>2200</v>
+      </c>
+      <c r="AL94">
+        <v>2500</v>
+      </c>
+      <c r="AM94">
+        <v>2600</v>
+      </c>
+      <c r="AN94" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO94" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP94">
+        <v>1398</v>
+      </c>
+      <c r="AQ94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="2:43" ht="98" x14ac:dyDescent="0.25">
+      <c r="B95">
+        <v>94</v>
+      </c>
+      <c r="D95">
+        <v>1400</v>
+      </c>
+      <c r="F95" s="1">
+        <v>1.38888888888889E-3</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="I95" s="1">
+        <v>7.6388888888888904E-3</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95" t="s">
+        <v>169</v>
+      </c>
+      <c r="M95" s="1">
+        <v>1.38888888888889E-2</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q95" s="1">
+        <v>2.8472222222222201E-2</v>
+      </c>
+      <c r="R95">
+        <v>1</v>
+      </c>
+      <c r="S95" t="s">
+        <v>426</v>
+      </c>
+      <c r="T95" t="s">
+        <v>427</v>
+      </c>
+      <c r="U95" s="1">
+        <v>4.3749999999999997E-2</v>
+      </c>
+      <c r="V95">
+        <v>1</v>
+      </c>
+      <c r="W95" t="s">
+        <v>428</v>
+      </c>
+      <c r="X95" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+      <c r="AA95" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB95" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC95" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD95">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF95" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG95">
+        <v>800</v>
+      </c>
+      <c r="AH95">
+        <v>1700</v>
+      </c>
+      <c r="AI95">
+        <v>1500</v>
+      </c>
+      <c r="AJ95">
+        <v>1900</v>
+      </c>
+      <c r="AK95">
+        <v>2200</v>
+      </c>
+      <c r="AL95">
+        <v>2800</v>
+      </c>
+      <c r="AM95">
+        <v>2600</v>
+      </c>
+      <c r="AN95" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO95" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP95">
+        <v>1400</v>
+      </c>
+      <c r="AQ95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B96">
+        <v>95</v>
+      </c>
+      <c r="D96">
+        <v>1418</v>
+      </c>
+      <c r="E96" t="s">
+        <v>30</v>
+      </c>
+      <c r="F96" s="1">
+        <v>4.1666666666666701E-3</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="I96" s="1">
+        <v>2.36111111111111E-2</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+      <c r="K96" t="s">
+        <v>431</v>
+      </c>
+      <c r="M96" s="1">
+        <v>3.2638888888888898E-2</v>
+      </c>
+      <c r="N96">
+        <v>2</v>
+      </c>
+      <c r="O96" t="s">
+        <v>169</v>
+      </c>
+      <c r="P96" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>22</v>
+      </c>
+      <c r="R96">
+        <v>-1</v>
+      </c>
+      <c r="U96" t="s">
+        <v>22</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB96" t="s">
+        <v>433</v>
+      </c>
+      <c r="AC96" s="1">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="AD96">
+        <v>1</v>
+      </c>
+      <c r="AE96" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF96" t="s">
+        <v>176</v>
+      </c>
+      <c r="AG96">
+        <v>1000</v>
+      </c>
+      <c r="AH96">
+        <v>1300</v>
+      </c>
+      <c r="AI96">
+        <v>1500</v>
+      </c>
+      <c r="AJ96">
+        <v>2100</v>
+      </c>
+      <c r="AK96">
+        <v>2400</v>
+      </c>
+      <c r="AL96">
+        <v>3000</v>
+      </c>
+      <c r="AM96">
+        <v>2500</v>
+      </c>
+      <c r="AN96" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO96" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP96">
+        <v>1418</v>
+      </c>
+      <c r="AQ96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="2:43" ht="140" x14ac:dyDescent="0.25">
+      <c r="B97">
+        <v>96</v>
+      </c>
+      <c r="D97">
+        <v>1430</v>
+      </c>
+      <c r="F97" s="1">
+        <v>2.0833333333333298E-3</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="I97" s="1">
+        <v>4.8611111111111103E-3</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97" t="s">
+        <v>434</v>
+      </c>
+      <c r="L97" t="s">
+        <v>435</v>
+      </c>
+      <c r="M97" s="1">
+        <v>1.7361111111111101E-2</v>
+      </c>
+      <c r="N97">
+        <v>2</v>
+      </c>
+      <c r="O97" t="s">
+        <v>436</v>
+      </c>
+      <c r="P97" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q97" s="1">
+        <v>3.2638888888888898E-2</v>
+      </c>
+      <c r="R97">
+        <v>1</v>
+      </c>
+      <c r="S97" t="s">
+        <v>438</v>
+      </c>
+      <c r="T97" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="U97" s="1">
+        <v>4.5138888888888902E-2</v>
+      </c>
+      <c r="V97">
+        <v>1</v>
+      </c>
+      <c r="W97" t="s">
+        <v>244</v>
+      </c>
+      <c r="X97" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z97">
+        <v>-1</v>
+      </c>
+      <c r="AA97" t="s">
+        <v>441</v>
+      </c>
+      <c r="AB97" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="AC97" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD97">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF97" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG97">
+        <v>900</v>
+      </c>
+      <c r="AH97">
+        <v>800</v>
+      </c>
+      <c r="AI97">
+        <v>1000</v>
+      </c>
+      <c r="AJ97">
+        <v>1700</v>
+      </c>
+      <c r="AK97">
+        <v>1900</v>
+      </c>
+      <c r="AL97">
+        <v>2600</v>
+      </c>
+      <c r="AM97">
+        <v>2600</v>
+      </c>
+      <c r="AN97" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO97" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP97">
+        <v>1430</v>
+      </c>
+      <c r="AQ97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="2:43" ht="56" x14ac:dyDescent="0.25">
+      <c r="B98">
+        <v>97</v>
+      </c>
+      <c r="D98">
+        <v>1437</v>
+      </c>
+      <c r="F98" s="1">
+        <v>2.0833333333333298E-3</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="I98" s="1">
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98" t="s">
+        <v>443</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="M98" s="1">
+        <v>1.38888888888889E-2</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98" t="s">
+        <v>445</v>
+      </c>
+      <c r="P98" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q98" s="1">
+        <v>3.4722222222222203E-2</v>
+      </c>
+      <c r="R98">
+        <v>2</v>
+      </c>
+      <c r="S98" t="s">
+        <v>447</v>
+      </c>
+      <c r="T98" t="s">
+        <v>448</v>
+      </c>
+      <c r="U98" s="1">
+        <v>5.9722222222222197E-2</v>
+      </c>
+      <c r="V98">
+        <v>2</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+      <c r="AA98" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB98" t="s">
+        <v>449</v>
+      </c>
+      <c r="AC98" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD98">
+        <v>-2</v>
+      </c>
+      <c r="AE98" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF98" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG98">
+        <v>800</v>
+      </c>
+      <c r="AH98">
+        <v>1200</v>
+      </c>
+      <c r="AI98">
+        <v>1800</v>
+      </c>
+      <c r="AJ98">
+        <v>1600</v>
+      </c>
+      <c r="AK98">
+        <v>2200</v>
+      </c>
+      <c r="AL98">
+        <v>2600</v>
+      </c>
+      <c r="AM98">
+        <v>2600</v>
+      </c>
+      <c r="AN98" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO98" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP98">
+        <v>1437</v>
+      </c>
+      <c r="AQ98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="2:43" ht="42" x14ac:dyDescent="0.25">
+      <c r="B99">
+        <v>98</v>
+      </c>
+      <c r="D99">
+        <v>1452</v>
+      </c>
+      <c r="F99" s="1">
+        <v>1.38888888888889E-3</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99" t="s">
+        <v>450</v>
+      </c>
+      <c r="I99" s="1">
+        <v>2.4305555555555601E-2</v>
+      </c>
+      <c r="J99">
+        <v>2</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="M99" s="1">
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="O99" t="s">
+        <v>451</v>
+      </c>
+      <c r="P99" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q99" s="1">
+        <v>5.6944444444444402E-2</v>
+      </c>
+      <c r="R99">
+        <v>1</v>
+      </c>
+      <c r="S99" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="T99" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="U99" t="s">
+        <v>22</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="AB99" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD99">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF99" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="AG99">
+        <v>800</v>
+      </c>
+      <c r="AH99">
+        <v>1400</v>
+      </c>
+      <c r="AI99">
+        <v>800</v>
+      </c>
+      <c r="AJ99">
+        <v>1600</v>
+      </c>
+      <c r="AK99">
+        <v>2500</v>
+      </c>
+      <c r="AL99">
+        <v>2900</v>
+      </c>
+      <c r="AM99">
+        <v>2700</v>
+      </c>
+      <c r="AN99" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO99" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP99">
+        <v>1452</v>
+      </c>
+      <c r="AQ99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="2:43" ht="42" x14ac:dyDescent="0.25">
+      <c r="B100">
+        <v>99</v>
+      </c>
+      <c r="D100">
+        <v>1455</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="I100" t="s">
+        <v>453</v>
+      </c>
+      <c r="M100" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q100" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="S100" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="T100" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="U100" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="W100" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="X100" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="Y100" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AC100" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AE100" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF100" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="AG100">
+        <v>800</v>
+      </c>
+      <c r="AH100">
+        <v>1200</v>
+      </c>
+      <c r="AI100">
+        <v>1100</v>
+      </c>
+      <c r="AJ100">
+        <v>1600</v>
+      </c>
+      <c r="AK100">
+        <v>2400</v>
+      </c>
+      <c r="AL100">
+        <v>2800</v>
+      </c>
+      <c r="AM100">
+        <v>2900</v>
+      </c>
+      <c r="AN100" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO100" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP100">
+        <v>1455</v>
+      </c>
+      <c r="AQ100">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/edu.xlsx
+++ b/edu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18319\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B3BC1F-65FB-45F4-BB92-F9DA3CEE5238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5F8BA-DD86-4A4B-B4B0-464ECFC8AF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="507">
   <si>
     <t>种类</t>
   </si>
@@ -1944,6 +1944,221 @@
   </si>
   <si>
     <t>淀粉质+？？？</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>贪心，构造</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>构造，链的构造</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">假设在第 i 次操作时，真正起作用的中间变量是 xi
+i=1 x1=a2   a3= a3-x1/a3+x1
+i=2 x2=a3-x1/a3+x1
+xi = a{i+1} +- x{i-1}
+如果x{i-1}!=0 那么 a{i+1}-x{i-1}和a{i+1}+x{i-1}是不同的两个数字
+如果=0 那么这俩一样 只进行一次转移
+dp[i][j] 表示第 i 步时，中间变量 xi 的值为 j - BASE 方案数 </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>动态规划DP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>贪心</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数论，枚举，区间加</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>假设 有一个k是j j*c如果刚好大于等于bi 并且小于ai 那么当前数字就是不可以的
+处理不合法的位置 剩下的位置就都是合法的了</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大流+置换环+DFS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个置换环显然可以剩下其中一个不移走，考虑不同环直接可能可以都由同一个不移走，这里次数会-1，就是最大匹配问题了</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>贪心排序</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>贪心观察</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>就是最后的顺序肯定是固定的
+当前放的顺序肯定也是固定的，先是中间的两个元素往外放
+然后-1 +1的元素往外放，这里本来就能连续的一直拓展的
+就不用操作了</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>字符串哈希，状压，map</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录位置，根据位置预处理存在的长度为1-10的哈希，每次根据读入匹配当前就是的哈希就行</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数论，枚举，二分</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>假设因数 d 在 i 行 j 列 那么就是 i * j = d， i 一定是 d 的因数， d 是 m 的因数， 那么 i 一定也是 m 的因数， 所以行号肯定在因数数组里面 
+    对于某个合法因数d 合法的行号 i 得满足这些条件
+    i &lt;= n &amp;&amp; d/i &lt;= n  -&gt; i &gt;= d/n (向上取整)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>枚举</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>贪心+排序</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>计数DP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">设 dp i,j 当前处理到前 i 个字符，且以第 i 个字符结尾的极大连续相同段是从第 j 个字符开始的，此时合法的方案数
+j-1 != j
+dp i,j 表示 [j,i] 为一个极大连续段时，[1,i] 的方案数
+k &lt; j 的时候 aki=2 从前面转移过来 得分段了 ， k &gt;= j 的时候从后面转移过来 必须一致 aki=1
+</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>猜结论+简单分析</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次大规则或者少规则，干掉的人都要*2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大独立集，最小点覆盖，dp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">相邻的两个位置必须至少选中一个位置的，所以颜色也必须选一个，问题转为40个点，
+有很多带权点，选最少的点权和覆盖整张图，最小点覆盖=全集-最大独立集
+可以考虑分20+20个 大的20爆搜 小的20dp存数组，这里是不断减少颜色集合
+也可以考虑直接暴力dfs减少集合去做，复杂度是对的 
+</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>简单构造 贪心</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">   dp[i][j] 当前在ij了 当前开始拐弯 需要的最小时间
+   dp[i][j] + 1 &gt;= a[i][j + 1] + 1;
+   dp[i][j] &gt;= a[i][j + 1]
+   dp[i][j] + 1 &gt;= dp[i][j + 1]
+   dp[i][j] &gt;= dp[i][j + 1] - 1;
+   dp[i][j] + (m - j) * 2 + 1 &gt;= a[1 - i][j] + 1;
+   dp[i][j] &gt;= a[1 - i][j] - (m - j) * 2;
+dp[0][m] = a[1][m]; /*dp[i][j] &gt;= a[1 - i][j] - (m - j) * 2;*/</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>计数dp 背包</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>因为每次都要物品体积+1，所以本质是一个等差数列，最多根号个物品就i满了
+考虑暴力是枚举几个物品，这里可以想到01背包和完全背包的性质，用完全背包优化
+这里时间复杂度满足了，空间还有点问题，考虑用滚动数组优化一下，每次算完累加到ans数组上
+因为这里dp数组会清空</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>线段树pushup，最大子段和</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>这题，先手画一下图发现，更改的就是某一层的全部左右儿子swap一下就行，这里由于是
+可持久化的，因为n不大，考虑预处理全部状态对应的最大子段和答案，枚举的状态是
+哪些层的左右儿子要交换，考虑二进制状态10100101，有1的位置对应的层的swap就行
+答案经过pushup后记录即可</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>斯特林数，数论，组合数学</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>构造诈骗</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>贪心模拟，手写一下几种情况就行</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>观察到每一次打怪都能明确一段1-x的区间，有很多段区间，如果之间有相交交错该怎么办呢？
+考虑如果是包含之类的 就直接更新成大的那个线段就行，如果没有交点就不管，
+如果有一段交错了，考虑min max端点更新即可</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SET或者啥模拟</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>观察 二进制LOG的性质 枚举</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果枚举两段的话 可以三段都直接算出来，复杂度n方，考虑怎么优化呢
+考虑枚举其中一段前缀，后缀可以分成两段，由于要求2的i次方，
+枚举i的大小 考虑第三段刚好小于等于这个2的i次方大小的 这里是贪心思想 考虑二分后缀和实现 
+最后剩下的就是第二段了 ，双log复杂度</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>树型DP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合数学</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>三种情况当前u节点合法：
+1.当前u就是黑色节点
+2.当前u的周围有刚好距离=1的点有黑色节点
+3.当前u的周围有刚好距离=1的点 是合法点并且这个合法点的子树内黑色节点&gt;=2
+考虑设计状态son是和u相邻的点 有多少点是合法点 
+这里是v可以就是黑点 或者 v可以到达黑点并且v的siz&gt;=2
+换根dp就行了，col[u] == 1 || son[u] &gt; 0 ，ans[u] = 1;
+考虑u往v变的时候 ，v会不会作为u的贡献son 如果会的话 -- dfs后 ++
+考虑 u会不会作为v的贡献son，u得是v的有效邻居并且 siz1-sizv&gt;=2 （siz是黑色点）
+ ，col[u] == 1 || son[u] &gt; 0&amp;&amp;siz1-sizv&gt;=2，如果会的话sonv ++</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2335,19 +2550,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ100"/>
+  <dimension ref="A1:AQ157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="8" max="8" width="62.54296875" customWidth="1"/>
     <col min="11" max="11" width="21.453125" customWidth="1"/>
-    <col min="12" max="12" width="54.7265625" customWidth="1"/>
+    <col min="12" max="12" width="90.54296875" customWidth="1"/>
     <col min="13" max="13" width="10.08984375" customWidth="1"/>
     <col min="15" max="15" width="25.6328125" customWidth="1"/>
-    <col min="16" max="16" width="70.90625" customWidth="1"/>
+    <col min="16" max="16" width="90.81640625" customWidth="1"/>
     <col min="17" max="17" width="13.7265625" customWidth="1"/>
     <col min="19" max="19" width="40.08984375" customWidth="1"/>
-    <col min="20" max="20" width="79.7265625" customWidth="1"/>
+    <col min="20" max="20" width="87.90625" customWidth="1"/>
     <col min="23" max="23" width="34.90625" customWidth="1"/>
     <col min="24" max="24" width="145.36328125" customWidth="1"/>
     <col min="25" max="25" width="12.36328125" customWidth="1"/>
@@ -2355,7 +2570,7 @@
     <col min="28" max="28" width="83.453125" customWidth="1"/>
     <col min="30" max="30" width="7.7265625" customWidth="1"/>
     <col min="31" max="31" width="18.7265625" customWidth="1"/>
-    <col min="32" max="32" width="15" customWidth="1"/>
+    <col min="32" max="32" width="17.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -6246,7 +6461,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:43" ht="28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" ht="27.5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -8426,7 +8641,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="2:43" ht="56" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:43" ht="42" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>76</v>
       </c>
@@ -10886,7 +11101,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="2:43" ht="56" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:43" ht="42" x14ac:dyDescent="0.25">
       <c r="B98">
         <v>97</v>
       </c>
@@ -11187,6 +11402,786 @@
       </c>
       <c r="AQ100">
         <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="2:43" ht="154" x14ac:dyDescent="0.25">
+      <c r="B122">
+        <v>121</v>
+      </c>
+      <c r="D122">
+        <v>1626</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+      <c r="H122" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="I122" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="L122" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="M122" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="N122">
+        <v>1</v>
+      </c>
+      <c r="O122" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="P122" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q122" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="R122">
+        <v>2</v>
+      </c>
+      <c r="S122" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="T122" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="U122" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="V122">
+        <v>1</v>
+      </c>
+      <c r="W122" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="AE122" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF122" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="AG122">
+        <v>800</v>
+      </c>
+      <c r="AH122">
+        <v>1100</v>
+      </c>
+      <c r="AI122">
+        <v>1700</v>
+      </c>
+      <c r="AJ122">
+        <v>2100</v>
+      </c>
+      <c r="AK122">
+        <v>2400</v>
+      </c>
+      <c r="AL122">
+        <v>2800</v>
+      </c>
+      <c r="AM122" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN122" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO122" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP122">
+        <v>1626</v>
+      </c>
+      <c r="AQ122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="2:43" ht="112" x14ac:dyDescent="0.25">
+      <c r="B134">
+        <v>133</v>
+      </c>
+      <c r="D134">
+        <v>1716</v>
+      </c>
+      <c r="E134" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="I134" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="K134" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="L134" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="M134" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="N134">
+        <v>2</v>
+      </c>
+      <c r="O134" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="P134" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q134" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="R134">
+        <v>4</v>
+      </c>
+      <c r="S134" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="T134" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="U134" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="V134">
+        <v>1</v>
+      </c>
+      <c r="W134" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="AE134" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF134" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="AG134">
+        <v>800</v>
+      </c>
+      <c r="AH134">
+        <v>800</v>
+      </c>
+      <c r="AI134">
+        <v>2000</v>
+      </c>
+      <c r="AJ134">
+        <v>2000</v>
+      </c>
+      <c r="AK134">
+        <v>2500</v>
+      </c>
+      <c r="AL134">
+        <v>2500</v>
+      </c>
+      <c r="AM134" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN134" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO134" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP134">
+        <v>1716</v>
+      </c>
+      <c r="AQ134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="2:43" ht="84" x14ac:dyDescent="0.25">
+      <c r="B141">
+        <v>140</v>
+      </c>
+      <c r="D141">
+        <v>1767</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="G141">
+        <v>2</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="I141" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="J141">
+        <v>2</v>
+      </c>
+      <c r="K141" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="L141" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="M141" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="O141" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="P141" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q141" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="R141">
+        <v>2</v>
+      </c>
+      <c r="S141" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="T141" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="U141" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="V141">
+        <v>3</v>
+      </c>
+      <c r="AE141" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF141" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="AG141">
+        <v>800</v>
+      </c>
+      <c r="AH141">
+        <v>800</v>
+      </c>
+      <c r="AI141">
+        <v>2100</v>
+      </c>
+      <c r="AJ141">
+        <v>1500</v>
+      </c>
+      <c r="AK141">
+        <v>2500</v>
+      </c>
+      <c r="AL141">
+        <v>3100</v>
+      </c>
+      <c r="AM141" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN141" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO141" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP141">
+        <v>1767</v>
+      </c>
+      <c r="AQ141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="2:43" ht="112" x14ac:dyDescent="0.25">
+      <c r="B142">
+        <v>141</v>
+      </c>
+      <c r="D142">
+        <v>1783</v>
+      </c>
+      <c r="E142" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="G142">
+        <v>2</v>
+      </c>
+      <c r="H142" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="I142" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="M142" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="N142">
+        <v>2</v>
+      </c>
+      <c r="O142" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="P142" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q142" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="R142">
+        <v>2</v>
+      </c>
+      <c r="S142" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="T142" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="U142" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="V142">
+        <v>1</v>
+      </c>
+      <c r="W142" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="X142" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="Y142" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="Z142">
+        <v>4</v>
+      </c>
+      <c r="AE142" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF142" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="AG142">
+        <v>800</v>
+      </c>
+      <c r="AH142">
+        <v>1100</v>
+      </c>
+      <c r="AI142">
+        <v>1700</v>
+      </c>
+      <c r="AJ142">
+        <v>2000</v>
+      </c>
+      <c r="AK142">
+        <v>2300</v>
+      </c>
+      <c r="AL142">
+        <v>2500</v>
+      </c>
+      <c r="AM142">
+        <v>2800</v>
+      </c>
+      <c r="AN142" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO142" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP142">
+        <v>1783</v>
+      </c>
+      <c r="AQ142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="2:43" ht="56" x14ac:dyDescent="0.25">
+      <c r="B143">
+        <v>142</v>
+      </c>
+      <c r="D143">
+        <v>1792</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="G143">
+        <v>2</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="I143" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="J143">
+        <v>1</v>
+      </c>
+      <c r="K143" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="L143" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="M143" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="N143">
+        <v>2</v>
+      </c>
+      <c r="O143" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="P143" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q143" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="R143">
+        <v>2</v>
+      </c>
+      <c r="S143" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="T143" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="U143" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="V143">
+        <v>1</v>
+      </c>
+      <c r="AE143" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF143" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="AG143">
+        <v>800</v>
+      </c>
+      <c r="AH143">
+        <v>1200</v>
+      </c>
+      <c r="AI143">
+        <v>1500</v>
+      </c>
+      <c r="AJ143">
+        <v>1700</v>
+      </c>
+      <c r="AK143">
+        <v>2400</v>
+      </c>
+      <c r="AL143">
+        <v>2700</v>
+      </c>
+      <c r="AM143">
+        <v>2900</v>
+      </c>
+      <c r="AN143" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO143" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP143">
+        <v>1792</v>
+      </c>
+      <c r="AQ143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18319\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5F8BA-DD86-4A4B-B4B0-464ECFC8AF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E24BF31-AA94-44F8-930A-CA50D5E57ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="515">
   <si>
     <t>种类</t>
   </si>
@@ -2159,6 +2159,43 @@
 考虑u往v变的时候 ，v会不会作为u的贡献son 如果会的话 -- dfs后 ++
 考虑 u会不会作为v的贡献son，u得是v的有效邻居并且 siz1-sizv&gt;=2 （siz是黑色点）
  ，col[u] == 1 || son[u] &gt; 0&amp;&amp;siz1-sizv&gt;=2，如果会的话sonv ++</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>二进制 贪心 模拟</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">模拟 </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>前缀和 贪心 观察</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> L: 这段运动开始时的位置
+ R: 这段运动的目标位置
+ stT: 这段运动开始时间
+ edT: 这段运动结束时间</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">前缀的b里面的数字太多了 多出来的数字只能当小数字了 
+/前缀里面的非b里面的数字太多了 多出来的数字只能是大数字了 所以 
+</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>topo排序 缩点</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>题目约束的关系得是一些链，观察到，然后可以把这个关系给缩点，然后在原关系基础上建新的有向图，然后建图的时候如果俩都来自于同一个点，那就根据dep来看 是否合法，都合法后建图跑topo排序即可</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>子集DP</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -6580,7 +6617,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:43" ht="56" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43" ht="28" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -11334,15 +11371,27 @@
       <c r="F100" s="9" t="s">
         <v>454</v>
       </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
       <c r="I100" t="s">
         <v>453</v>
       </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
       <c r="M100" s="9" t="s">
         <v>454</v>
       </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
       <c r="Q100" s="9" t="s">
         <v>454</v>
       </c>
+      <c r="R100">
+        <v>1</v>
+      </c>
       <c r="S100" s="9" t="s">
         <v>456</v>
       </c>
@@ -11352,6 +11401,9 @@
       <c r="U100" s="9" t="s">
         <v>454</v>
       </c>
+      <c r="V100">
+        <v>1</v>
+      </c>
       <c r="W100" s="9" t="s">
         <v>458</v>
       </c>
@@ -11361,6 +11413,9 @@
       <c r="Y100" s="9" t="s">
         <v>454</v>
       </c>
+      <c r="Z100">
+        <v>1</v>
+      </c>
       <c r="AC100" s="9" t="s">
         <v>454</v>
       </c>
@@ -11404,9 +11459,93 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="2:43" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:43" ht="56" x14ac:dyDescent="0.25">
       <c r="B101">
         <v>100</v>
+      </c>
+      <c r="D101">
+        <v>1463</v>
+      </c>
+      <c r="E101" t="s">
+        <v>169</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="G101">
+        <v>2</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="I101" t="s">
+        <v>453</v>
+      </c>
+      <c r="J101">
+        <v>3</v>
+      </c>
+      <c r="K101" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="L101" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="M101" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="N101">
+        <v>2</v>
+      </c>
+      <c r="O101" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="P101" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q101" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="R101">
+        <v>2</v>
+      </c>
+      <c r="S101" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="T101" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="U101" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="V101">
+        <v>1</v>
+      </c>
+      <c r="W101" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="Y101" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE101" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="AF101" s="9" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="102" spans="2:43" x14ac:dyDescent="0.25">

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18319\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E24BF31-AA94-44F8-930A-CA50D5E57ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D112D2-47C7-4B43-BBB8-C0462A43B0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="527">
   <si>
     <t>种类</t>
   </si>
@@ -2181,21 +2181,78 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>topo排序 缩点</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>题目约束的关系得是一些链，观察到，然后可以把这个关系给缩点，然后在原关系基础上建新的有向图，然后建图的时候如果俩都来自于同一个点，那就根据dep来看 是否合法，都合法后建图跑topo排序即可</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>子集DP/式子推完后建图线性DP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>先证明存在最优解按 P=x+y 周期重复；
+于是每个周期位置 i 有权值 n/P+(i&lt;=n%P)，禁边在模 P 下等价为 i--i+x，
+图分成若干个环，对每个带权环做最大独立集并求和。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>？</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>贪心+栈</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>贪心 前后缀和</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>模拟</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>维护当前位置能到达的最高位置最低位置</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>大胆猜测+模拟</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">前缀的b里面的数字太多了 多出来的数字只能当小数字了 
-/前缀里面的非b里面的数字太多了 多出来的数字只能是大数字了 所以 
+前缀里面的非b里面的数字太多了 多出来的数字只能是大数字了 所以 
 </t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>topo排序 缩点</t>
+    <t>我的做法通过纸上手玩的方法 考虑最大的那个数字变成2，其他数字都变成1，
+这个是哪种方法都是一致的，考虑最后一个数字，如果在除以前面某个数字后，前面的某个数字
+能除以最大的这个数字仍然变成1，那么最大的那个数字就应该变小了，否则就最大的数字不变，
+只考虑操作小的数字除以大的数字
+朋友的做法是构造4，16，256，256*256的数字保留，然后最后的时候
+大的数字除以小的数字来变成小的数字，然后再除以一次变成1</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>题目约束的关系得是一些链，观察到，然后可以把这个关系给缩点，然后在原关系基础上建新的有向图，然后建图的时候如果俩都来自于同一个点，那就根据dep来看 是否合法，都合法后建图跑topo排序即可</t>
+    <t>状压+只枚举最多20位</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>子集DP</t>
+    <t>如果k&lt;=20,那么直接枚举全部存在的状态，当前状态的取反肯定是取不到的
+如果k很大，那么肯定是存在合法状态的，因为2^20已经超过1e6了，就最多n种取不到
+然后就确定了前面k-20位都是0，最后20位枚举一下状态就行</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>树上问题</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -11416,6 +11473,12 @@
       <c r="Z100">
         <v>1</v>
       </c>
+      <c r="AA100" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="AB100" s="9" t="s">
+        <v>516</v>
+      </c>
       <c r="AC100" s="9" t="s">
         <v>454</v>
       </c>
@@ -11500,7 +11563,7 @@
         <v>509</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="Q101" s="9" t="s">
         <v>454</v>
@@ -11509,10 +11572,10 @@
         <v>2</v>
       </c>
       <c r="S101" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="T101" s="10" t="s">
         <v>512</v>
-      </c>
-      <c r="T101" s="10" t="s">
-        <v>513</v>
       </c>
       <c r="U101" s="9" t="s">
         <v>454</v>
@@ -11523,33 +11586,177 @@
       <c r="W101" s="9" t="s">
         <v>514</v>
       </c>
+      <c r="X101" s="10" t="s">
+        <v>515</v>
+      </c>
       <c r="Y101" s="9" t="s">
         <v>454</v>
       </c>
       <c r="Z101">
+        <v>1</v>
+      </c>
+      <c r="AA101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE101" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF101" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="AG101">
+        <v>1100</v>
+      </c>
+      <c r="AH101">
+        <v>1400</v>
+      </c>
+      <c r="AI101">
+        <v>1800</v>
+      </c>
+      <c r="AJ101">
+        <v>1900</v>
+      </c>
+      <c r="AK101">
+        <v>2400</v>
+      </c>
+      <c r="AL101">
+        <v>3100</v>
+      </c>
+      <c r="AM101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO101" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP101">
+        <v>1463</v>
+      </c>
+      <c r="AQ101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="2:43" ht="84" x14ac:dyDescent="0.25">
+      <c r="B102">
+        <v>101</v>
+      </c>
+      <c r="D102">
+        <v>1496</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="I102" t="s">
+        <v>453</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="L102" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="M102" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="N102">
+        <v>1</v>
+      </c>
+      <c r="O102" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="P102" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="Q102" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="R102">
+        <v>1</v>
+      </c>
+      <c r="S102" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="T102" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="U102" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="V102">
+        <v>1</v>
+      </c>
+      <c r="W102" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="X102" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z102">
         <v>0</v>
       </c>
-      <c r="AA101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE101" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="AF101" s="9" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="102" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B102">
+      <c r="AA102" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB102" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG102">
+        <v>1000</v>
+      </c>
+      <c r="AH102">
+        <v>1000</v>
+      </c>
+      <c r="AI102">
+        <v>1600</v>
+      </c>
+      <c r="AJ102">
+        <v>1700</v>
+      </c>
+      <c r="AK102">
+        <v>2400</v>
+      </c>
+      <c r="AL102">
+        <v>2600</v>
+      </c>
+      <c r="AM102" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN102" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO102" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP102">
+        <v>1496</v>
+      </c>
+      <c r="AQ102">
         <v>101</v>
       </c>
     </row>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18319\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D112D2-47C7-4B43-BBB8-C0462A43B0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA2208E-5DDF-4E14-9751-C085076F0033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="537">
   <si>
     <t>种类</t>
   </si>
@@ -2253,6 +2253,49 @@
   </si>
   <si>
     <t>树上问题</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>枚举因子是合法最小单位 check</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>构造</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>很难</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>线段树</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>push维护一个前缀，维护前缀和和区间minmax上下界即可</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>最短路dij+状压维护minmax存在过的</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>dij跑当前dpu00,表示当前在u点，已经有无经过min max的点，的最短路径
+这题和之前那个好几个维度的单点修线段树的题本质一样的，都是状压维护全部情况
+题目合法的情况就是最优的</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLOW 最大闭合权子图问题</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑2和1，选2了那就肯定得选1，所以建边2-&gt;1，然后这样建最大闭合权子图边太多了，考虑对值域统一考虑，存一个每个值域存过的上一个位置的lst
+只考虑在之前lst的基础上建即可，去除无用边</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>多项式范德蒙德卷积</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -11726,6 +11769,18 @@
       <c r="AB102" t="s">
         <v>25</v>
       </c>
+      <c r="AC102" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD102" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE102" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF102" s="9" t="s">
+        <v>497</v>
+      </c>
       <c r="AG102">
         <v>1000</v>
       </c>
@@ -11760,8 +11815,128 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="2:43" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:43" ht="42" x14ac:dyDescent="0.25">
       <c r="B103">
+        <v>102</v>
+      </c>
+      <c r="D103">
+        <v>1473</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="I103" t="s">
+        <v>453</v>
+      </c>
+      <c r="J103">
+        <v>1</v>
+      </c>
+      <c r="K103" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="L103" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="M103" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="P103" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="Q103" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="R103">
+        <v>1</v>
+      </c>
+      <c r="S103" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="T103" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="U103" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="V103">
+        <v>1</v>
+      </c>
+      <c r="W103" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="X103" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="Y103" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="Z103">
+        <v>1</v>
+      </c>
+      <c r="AA103" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="AB103" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="AC103" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD103">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF103" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="AG103">
+        <v>800</v>
+      </c>
+      <c r="AH103">
+        <v>1000</v>
+      </c>
+      <c r="AI103">
+        <v>1500</v>
+      </c>
+      <c r="AJ103">
+        <v>1700</v>
+      </c>
+      <c r="AK103">
+        <v>2400</v>
+      </c>
+      <c r="AL103">
+        <v>2700</v>
+      </c>
+      <c r="AM103">
+        <v>2800</v>
+      </c>
+      <c r="AN103" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO103" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP103">
+        <v>1473</v>
+      </c>
+      <c r="AQ103">
         <v>102</v>
       </c>
     </row>

--- a/edu.xlsx
+++ b/edu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18319\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA2208E-5DDF-4E14-9751-C085076F0033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F169A917-84E2-4C60-8AB2-AC90EB7EE28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="465">
   <si>
     <t>种类</t>
   </si>
@@ -1944,358 +1944,6 @@
   </si>
   <si>
     <t>淀粉质+？？？</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>贪心，构造</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>构造，链的构造</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">假设在第 i 次操作时，真正起作用的中间变量是 xi
-i=1 x1=a2   a3= a3-x1/a3+x1
-i=2 x2=a3-x1/a3+x1
-xi = a{i+1} +- x{i-1}
-如果x{i-1}!=0 那么 a{i+1}-x{i-1}和a{i+1}+x{i-1}是不同的两个数字
-如果=0 那么这俩一样 只进行一次转移
-dp[i][j] 表示第 i 步时，中间变量 xi 的值为 j - BASE 方案数 </t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>动态规划DP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>贪心</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>数论，枚举，区间加</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>假设 有一个k是j j*c如果刚好大于等于bi 并且小于ai 那么当前数字就是不可以的
-处理不合法的位置 剩下的位置就都是合法的了</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大流+置换环+DFS</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>每个置换环显然可以剩下其中一个不移走，考虑不同环直接可能可以都由同一个不移走，这里次数会-1，就是最大匹配问题了</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>贪心排序</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>贪心观察</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>就是最后的顺序肯定是固定的
-当前放的顺序肯定也是固定的，先是中间的两个元素往外放
-然后-1 +1的元素往外放，这里本来就能连续的一直拓展的
-就不用操作了</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>字符串哈希，状压，map</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>记录位置，根据位置预处理存在的长度为1-10的哈希，每次根据读入匹配当前就是的哈希就行</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>数论，枚举，二分</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>假设因数 d 在 i 行 j 列 那么就是 i * j = d， i 一定是 d 的因数， d 是 m 的因数， 那么 i 一定也是 m 的因数， 所以行号肯定在因数数组里面 
-    对于某个合法因数d 合法的行号 i 得满足这些条件
-    i &lt;= n &amp;&amp; d/i &lt;= n  -&gt; i &gt;= d/n (向上取整)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>枚举</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>贪心+排序</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>计数DP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">设 dp i,j 当前处理到前 i 个字符，且以第 i 个字符结尾的极大连续相同段是从第 j 个字符开始的，此时合法的方案数
-j-1 != j
-dp i,j 表示 [j,i] 为一个极大连续段时，[1,i] 的方案数
-k &lt; j 的时候 aki=2 从前面转移过来 得分段了 ， k &gt;= j 的时候从后面转移过来 必须一致 aki=1
-</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>猜结论+简单分析</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次大规则或者少规则，干掉的人都要*2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大独立集，最小点覆盖，dp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">相邻的两个位置必须至少选中一个位置的，所以颜色也必须选一个，问题转为40个点，
-有很多带权点，选最少的点权和覆盖整张图，最小点覆盖=全集-最大独立集
-可以考虑分20+20个 大的20爆搜 小的20dp存数组，这里是不断减少颜色集合
-也可以考虑直接暴力dfs减少集合去做，复杂度是对的 
-</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>简单构造 贪心</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">   dp[i][j] 当前在ij了 当前开始拐弯 需要的最小时间
-   dp[i][j] + 1 &gt;= a[i][j + 1] + 1;
-   dp[i][j] &gt;= a[i][j + 1]
-   dp[i][j] + 1 &gt;= dp[i][j + 1]
-   dp[i][j] &gt;= dp[i][j + 1] - 1;
-   dp[i][j] + (m - j) * 2 + 1 &gt;= a[1 - i][j] + 1;
-   dp[i][j] &gt;= a[1 - i][j] - (m - j) * 2;
-dp[0][m] = a[1][m]; /*dp[i][j] &gt;= a[1 - i][j] - (m - j) * 2;*/</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>计数dp 背包</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>因为每次都要物品体积+1，所以本质是一个等差数列，最多根号个物品就i满了
-考虑暴力是枚举几个物品，这里可以想到01背包和完全背包的性质，用完全背包优化
-这里时间复杂度满足了，空间还有点问题，考虑用滚动数组优化一下，每次算完累加到ans数组上
-因为这里dp数组会清空</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>线段树pushup，最大子段和</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>这题，先手画一下图发现，更改的就是某一层的全部左右儿子swap一下就行，这里由于是
-可持久化的，因为n不大，考虑预处理全部状态对应的最大子段和答案，枚举的状态是
-哪些层的左右儿子要交换，考虑二进制状态10100101，有1的位置对应的层的swap就行
-答案经过pushup后记录即可</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>斯特林数，数论，组合数学</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>F</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>构造诈骗</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>贪心模拟，手写一下几种情况就行</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>观察到每一次打怪都能明确一段1-x的区间，有很多段区间，如果之间有相交交错该怎么办呢？
-考虑如果是包含之类的 就直接更新成大的那个线段就行，如果没有交点就不管，
-如果有一段交错了，考虑min max端点更新即可</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SET或者啥模拟</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>观察 二进制LOG的性质 枚举</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果枚举两段的话 可以三段都直接算出来，复杂度n方，考虑怎么优化呢
-考虑枚举其中一段前缀，后缀可以分成两段，由于要求2的i次方，
-枚举i的大小 考虑第三段刚好小于等于这个2的i次方大小的 这里是贪心思想 考虑二分后缀和实现 
-最后剩下的就是第二段了 ，双log复杂度</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>树型DP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>组合数学</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>三种情况当前u节点合法：
-1.当前u就是黑色节点
-2.当前u的周围有刚好距离=1的点有黑色节点
-3.当前u的周围有刚好距离=1的点 是合法点并且这个合法点的子树内黑色节点&gt;=2
-考虑设计状态son是和u相邻的点 有多少点是合法点 
-这里是v可以就是黑点 或者 v可以到达黑点并且v的siz&gt;=2
-换根dp就行了，col[u] == 1 || son[u] &gt; 0 ，ans[u] = 1;
-考虑u往v变的时候 ，v会不会作为u的贡献son 如果会的话 -- dfs后 ++
-考虑 u会不会作为v的贡献son，u得是v的有效邻居并且 siz1-sizv&gt;=2 （siz是黑色点）
- ，col[u] == 1 || son[u] &gt; 0&amp;&amp;siz1-sizv&gt;=2，如果会的话sonv ++</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>二进制 贪心 模拟</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">模拟 </t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>前缀和 贪心 观察</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> L: 这段运动开始时的位置
- R: 这段运动的目标位置
- stT: 这段运动开始时间
- edT: 这段运动结束时间</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>topo排序 缩点</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>题目约束的关系得是一些链，观察到，然后可以把这个关系给缩点，然后在原关系基础上建新的有向图，然后建图的时候如果俩都来自于同一个点，那就根据dep来看 是否合法，都合法后建图跑topo排序即可</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>子集DP/式子推完后建图线性DP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>先证明存在最优解按 P=x+y 周期重复；
-于是每个周期位置 i 有权值 n/P+(i&lt;=n%P)，禁边在模 P 下等价为 i--i+x，
-图分成若干个环，对每个带权环做最大独立集并求和。</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>？</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>贪心+栈</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>贪心 前后缀和</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>模拟</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>维护当前位置能到达的最高位置最低位置</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>大胆猜测+模拟</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">前缀的b里面的数字太多了 多出来的数字只能当小数字了 
-前缀里面的非b里面的数字太多了 多出来的数字只能是大数字了 所以 
-</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>我的做法通过纸上手玩的方法 考虑最大的那个数字变成2，其他数字都变成1，
-这个是哪种方法都是一致的，考虑最后一个数字，如果在除以前面某个数字后，前面的某个数字
-能除以最大的这个数字仍然变成1，那么最大的那个数字就应该变小了，否则就最大的数字不变，
-只考虑操作小的数字除以大的数字
-朋友的做法是构造4，16，256，256*256的数字保留，然后最后的时候
-大的数字除以小的数字来变成小的数字，然后再除以一次变成1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>状压+只枚举最多20位</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果k&lt;=20,那么直接枚举全部存在的状态，当前状态的取反肯定是取不到的
-如果k很大，那么肯定是存在合法状态的，因为2^20已经超过1e6了，就最多n种取不到
-然后就确定了前面k-20位都是0，最后20位枚举一下状态就行</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>树上问题</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>枚举因子是合法最小单位 check</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>构造</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>很难</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>线段树</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>push维护一个前缀，维护前缀和和区间minmax上下界即可</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>最短路dij+状压维护minmax存在过的</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>dij跑当前dpu00,表示当前在u点，已经有无经过min max的点，的最短路径
-这题和之前那个好几个维度的单点修线段树的题本质一样的，都是状压维护全部情况
-题目合法的情况就是最优的</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>FLOW 最大闭合权子图问题</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>考虑2和1，选2了那就肯定得选1，所以建边2-&gt;1，然后这样建最大闭合权子图边太多了，考虑对值域统一考虑，存一个每个值域存过的上一个位置的lst
-只考虑在之前lst的基础上建即可，去除无用边</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>多项式范德蒙德卷积</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2687,19 +2335,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ157"/>
+  <dimension ref="A1:AQ100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="8" max="8" width="62.54296875" customWidth="1"/>
     <col min="11" max="11" width="21.453125" customWidth="1"/>
-    <col min="12" max="12" width="90.54296875" customWidth="1"/>
+    <col min="12" max="12" width="54.7265625" customWidth="1"/>
     <col min="13" max="13" width="10.08984375" customWidth="1"/>
     <col min="15" max="15" width="25.6328125" customWidth="1"/>
-    <col min="16" max="16" width="90.81640625" customWidth="1"/>
+    <col min="16" max="16" width="70.90625" customWidth="1"/>
     <col min="17" max="17" width="13.7265625" customWidth="1"/>
     <col min="19" max="19" width="40.08984375" customWidth="1"/>
-    <col min="20" max="20" width="87.90625" customWidth="1"/>
+    <col min="20" max="20" width="79.7265625" customWidth="1"/>
     <col min="23" max="23" width="34.90625" customWidth="1"/>
     <col min="24" max="24" width="145.36328125" customWidth="1"/>
     <col min="25" max="25" width="12.36328125" customWidth="1"/>
@@ -2707,7 +2355,7 @@
     <col min="28" max="28" width="83.453125" customWidth="1"/>
     <col min="30" max="30" width="7.7265625" customWidth="1"/>
     <col min="31" max="31" width="18.7265625" customWidth="1"/>
-    <col min="32" max="32" width="17.90625" customWidth="1"/>
+    <col min="32" max="32" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -6598,7 +6246,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:43" ht="27.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" ht="28" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -6717,7 +6365,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:43" ht="28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43" ht="56" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -8778,7 +8426,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="2:43" ht="42" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:43" ht="56" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>76</v>
       </c>
@@ -11238,7 +10886,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="2:43" ht="42" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:43" ht="56" x14ac:dyDescent="0.25">
       <c r="B98">
         <v>97</v>
       </c>
@@ -11471,27 +11119,15 @@
       <c r="F100" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="G100">
-        <v>1</v>
-      </c>
       <c r="I100" t="s">
         <v>453</v>
       </c>
-      <c r="J100">
-        <v>1</v>
-      </c>
       <c r="M100" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="N100">
-        <v>1</v>
-      </c>
       <c r="Q100" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="R100">
-        <v>1</v>
-      </c>
       <c r="S100" s="9" t="s">
         <v>456</v>
       </c>
@@ -11501,9 +11137,6 @@
       <c r="U100" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="V100">
-        <v>1</v>
-      </c>
       <c r="W100" s="9" t="s">
         <v>458</v>
       </c>
@@ -11513,15 +11146,6 @@
       <c r="Y100" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="Z100">
-        <v>1</v>
-      </c>
-      <c r="AA100" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="AB100" s="9" t="s">
-        <v>516</v>
-      </c>
       <c r="AC100" s="9" t="s">
         <v>454</v>
       </c>
@@ -11563,1146 +11187,6 @@
       </c>
       <c r="AQ100">
         <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="2:43" ht="56" x14ac:dyDescent="0.25">
-      <c r="B101">
-        <v>100</v>
-      </c>
-      <c r="D101">
-        <v>1463</v>
-      </c>
-      <c r="E101" t="s">
-        <v>169</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="G101">
-        <v>2</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="I101" t="s">
-        <v>453</v>
-      </c>
-      <c r="J101">
-        <v>3</v>
-      </c>
-      <c r="K101" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="L101" s="10" t="s">
-        <v>510</v>
-      </c>
-      <c r="M101" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="N101">
-        <v>2</v>
-      </c>
-      <c r="O101" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="P101" s="10" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q101" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="R101">
-        <v>2</v>
-      </c>
-      <c r="S101" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="T101" s="10" t="s">
-        <v>512</v>
-      </c>
-      <c r="U101" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="V101">
-        <v>1</v>
-      </c>
-      <c r="W101" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="X101" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="Y101" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="Z101">
-        <v>1</v>
-      </c>
-      <c r="AA101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE101" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="AF101" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="AG101">
-        <v>1100</v>
-      </c>
-      <c r="AH101">
-        <v>1400</v>
-      </c>
-      <c r="AI101">
-        <v>1800</v>
-      </c>
-      <c r="AJ101">
-        <v>1900</v>
-      </c>
-      <c r="AK101">
-        <v>2400</v>
-      </c>
-      <c r="AL101">
-        <v>3100</v>
-      </c>
-      <c r="AM101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO101" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP101">
-        <v>1463</v>
-      </c>
-      <c r="AQ101">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="2:43" ht="84" x14ac:dyDescent="0.25">
-      <c r="B102">
-        <v>101</v>
-      </c>
-      <c r="D102">
-        <v>1496</v>
-      </c>
-      <c r="E102" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="G102">
-        <v>1</v>
-      </c>
-      <c r="H102" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="I102" t="s">
-        <v>453</v>
-      </c>
-      <c r="J102">
-        <v>1</v>
-      </c>
-      <c r="K102" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="L102" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="M102" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="N102">
-        <v>1</v>
-      </c>
-      <c r="O102" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="P102" s="10" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q102" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="R102">
-        <v>1</v>
-      </c>
-      <c r="S102" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="T102" s="10" t="s">
-        <v>525</v>
-      </c>
-      <c r="U102" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="V102">
-        <v>1</v>
-      </c>
-      <c r="W102" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="X102" s="10" t="s">
-        <v>516</v>
-      </c>
-      <c r="Y102" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z102">
-        <v>0</v>
-      </c>
-      <c r="AA102" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB102" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC102" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD102" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE102" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="AF102" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="AG102">
-        <v>1000</v>
-      </c>
-      <c r="AH102">
-        <v>1000</v>
-      </c>
-      <c r="AI102">
-        <v>1600</v>
-      </c>
-      <c r="AJ102">
-        <v>1700</v>
-      </c>
-      <c r="AK102">
-        <v>2400</v>
-      </c>
-      <c r="AL102">
-        <v>2600</v>
-      </c>
-      <c r="AM102" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN102" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO102" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP102">
-        <v>1496</v>
-      </c>
-      <c r="AQ102">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="2:43" ht="42" x14ac:dyDescent="0.25">
-      <c r="B103">
-        <v>102</v>
-      </c>
-      <c r="D103">
-        <v>1473</v>
-      </c>
-      <c r="E103" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="G103">
-        <v>1</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="I103" t="s">
-        <v>453</v>
-      </c>
-      <c r="J103">
-        <v>1</v>
-      </c>
-      <c r="K103" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="L103" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="M103" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="N103">
-        <v>1</v>
-      </c>
-      <c r="O103" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="P103" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="Q103" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="R103">
-        <v>1</v>
-      </c>
-      <c r="S103" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="T103" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="U103" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="V103">
-        <v>1</v>
-      </c>
-      <c r="W103" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="X103" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="Y103" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="Z103">
-        <v>1</v>
-      </c>
-      <c r="AA103" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="AB103" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="AC103" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD103">
-        <v>0</v>
-      </c>
-      <c r="AE103" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="AF103" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="AG103">
-        <v>800</v>
-      </c>
-      <c r="AH103">
-        <v>1000</v>
-      </c>
-      <c r="AI103">
-        <v>1500</v>
-      </c>
-      <c r="AJ103">
-        <v>1700</v>
-      </c>
-      <c r="AK103">
-        <v>2400</v>
-      </c>
-      <c r="AL103">
-        <v>2700</v>
-      </c>
-      <c r="AM103">
-        <v>2800</v>
-      </c>
-      <c r="AN103" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO103" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP103">
-        <v>1473</v>
-      </c>
-      <c r="AQ103">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B104">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B105">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B106">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B107">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B108">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B109">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B110">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B111">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B112">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B113">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B114">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B115">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B116">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B117">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B118">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B119">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B120">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B121">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="2:43" ht="154" x14ac:dyDescent="0.25">
-      <c r="B122">
-        <v>121</v>
-      </c>
-      <c r="D122">
-        <v>1626</v>
-      </c>
-      <c r="E122" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="F122" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="G122">
-        <v>1</v>
-      </c>
-      <c r="H122" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="I122" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="J122">
-        <v>1</v>
-      </c>
-      <c r="K122" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="L122" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="M122" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="N122">
-        <v>1</v>
-      </c>
-      <c r="O122" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="P122" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="Q122" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="R122">
-        <v>2</v>
-      </c>
-      <c r="S122" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="T122" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="U122" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="V122">
-        <v>1</v>
-      </c>
-      <c r="W122" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="AE122" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="AF122" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="AG122">
-        <v>800</v>
-      </c>
-      <c r="AH122">
-        <v>1100</v>
-      </c>
-      <c r="AI122">
-        <v>1700</v>
-      </c>
-      <c r="AJ122">
-        <v>2100</v>
-      </c>
-      <c r="AK122">
-        <v>2400</v>
-      </c>
-      <c r="AL122">
-        <v>2800</v>
-      </c>
-      <c r="AM122" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN122" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO122" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP122">
-        <v>1626</v>
-      </c>
-      <c r="AQ122">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B123">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B124">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B125">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B126">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B127">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B128">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="129" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B129">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B130">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="131" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B131">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="132" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B132">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B133">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="134" spans="2:43" ht="112" x14ac:dyDescent="0.25">
-      <c r="B134">
-        <v>133</v>
-      </c>
-      <c r="D134">
-        <v>1716</v>
-      </c>
-      <c r="E134" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="F134" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="G134">
-        <v>1</v>
-      </c>
-      <c r="H134" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="I134" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="J134">
-        <v>1</v>
-      </c>
-      <c r="K134" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="L134" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="M134" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="N134">
-        <v>2</v>
-      </c>
-      <c r="O134" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="P134" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q134" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="R134">
-        <v>4</v>
-      </c>
-      <c r="S134" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="T134" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="U134" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="V134">
-        <v>1</v>
-      </c>
-      <c r="W134" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="AE134" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="AF134" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="AG134">
-        <v>800</v>
-      </c>
-      <c r="AH134">
-        <v>800</v>
-      </c>
-      <c r="AI134">
-        <v>2000</v>
-      </c>
-      <c r="AJ134">
-        <v>2000</v>
-      </c>
-      <c r="AK134">
-        <v>2500</v>
-      </c>
-      <c r="AL134">
-        <v>2500</v>
-      </c>
-      <c r="AM134" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN134" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO134" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP134">
-        <v>1716</v>
-      </c>
-      <c r="AQ134">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B135">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="136" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B136">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="137" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B137">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="138" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B138">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="139" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B139">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="140" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B140">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="141" spans="2:43" ht="84" x14ac:dyDescent="0.25">
-      <c r="B141">
-        <v>140</v>
-      </c>
-      <c r="D141">
-        <v>1767</v>
-      </c>
-      <c r="E141" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="F141" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="G141">
-        <v>2</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="I141" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="J141">
-        <v>2</v>
-      </c>
-      <c r="K141" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="L141" s="10" t="s">
-        <v>484</v>
-      </c>
-      <c r="M141" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="N141">
-        <v>1</v>
-      </c>
-      <c r="O141" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="P141" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q141" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="R141">
-        <v>2</v>
-      </c>
-      <c r="S141" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="T141" s="10" t="s">
-        <v>488</v>
-      </c>
-      <c r="U141" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="V141">
-        <v>3</v>
-      </c>
-      <c r="AE141" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="AF141" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="AG141">
-        <v>800</v>
-      </c>
-      <c r="AH141">
-        <v>800</v>
-      </c>
-      <c r="AI141">
-        <v>2100</v>
-      </c>
-      <c r="AJ141">
-        <v>1500</v>
-      </c>
-      <c r="AK141">
-        <v>2500</v>
-      </c>
-      <c r="AL141">
-        <v>3100</v>
-      </c>
-      <c r="AM141" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN141" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO141" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP141">
-        <v>1767</v>
-      </c>
-      <c r="AQ141">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="142" spans="2:43" ht="112" x14ac:dyDescent="0.25">
-      <c r="B142">
-        <v>141</v>
-      </c>
-      <c r="D142">
-        <v>1783</v>
-      </c>
-      <c r="E142" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="F142" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="G142">
-        <v>2</v>
-      </c>
-      <c r="H142" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="I142" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="J142">
-        <v>1</v>
-      </c>
-      <c r="K142" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="M142" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="N142">
-        <v>2</v>
-      </c>
-      <c r="O142" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="P142" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q142" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="R142">
-        <v>2</v>
-      </c>
-      <c r="S142" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="T142" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="U142" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="V142">
-        <v>1</v>
-      </c>
-      <c r="W142" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="X142" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="Y142" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="Z142">
-        <v>4</v>
-      </c>
-      <c r="AE142" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="AF142" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="AG142">
-        <v>800</v>
-      </c>
-      <c r="AH142">
-        <v>1100</v>
-      </c>
-      <c r="AI142">
-        <v>1700</v>
-      </c>
-      <c r="AJ142">
-        <v>2000</v>
-      </c>
-      <c r="AK142">
-        <v>2300</v>
-      </c>
-      <c r="AL142">
-        <v>2500</v>
-      </c>
-      <c r="AM142">
-        <v>2800</v>
-      </c>
-      <c r="AN142" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO142" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP142">
-        <v>1783</v>
-      </c>
-      <c r="AQ142">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="143" spans="2:43" ht="56" x14ac:dyDescent="0.25">
-      <c r="B143">
-        <v>142</v>
-      </c>
-      <c r="D143">
-        <v>1792</v>
-      </c>
-      <c r="E143" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="F143" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="G143">
-        <v>2</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="I143" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="J143">
-        <v>1</v>
-      </c>
-      <c r="K143" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="L143" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="M143" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="N143">
-        <v>2</v>
-      </c>
-      <c r="O143" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="P143" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="Q143" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="R143">
-        <v>2</v>
-      </c>
-      <c r="S143" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="T143" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="U143" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="V143">
-        <v>1</v>
-      </c>
-      <c r="AE143" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="AF143" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="AG143">
-        <v>800</v>
-      </c>
-      <c r="AH143">
-        <v>1200</v>
-      </c>
-      <c r="AI143">
-        <v>1500</v>
-      </c>
-      <c r="AJ143">
-        <v>1700</v>
-      </c>
-      <c r="AK143">
-        <v>2400</v>
-      </c>
-      <c r="AL143">
-        <v>2700</v>
-      </c>
-      <c r="AM143">
-        <v>2900</v>
-      </c>
-      <c r="AN143" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO143" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP143">
-        <v>1792</v>
-      </c>
-      <c r="AQ143">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="144" spans="2:43" x14ac:dyDescent="0.25">
-      <c r="B144">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B145">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B146">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B147">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B148">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B149">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B150">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B151">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B152">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B153">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B154">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B155">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B156">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B157">
-        <v>156</v>
       </c>
     </row>
   </sheetData>
